--- a/Strumenti/Schede_DnD_BX91.xlsx
+++ b/Strumenti/Schede_DnD_BX91.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Public\_Clienti\Maruga\Giochi\Vampiri\Vault\Vampiri\Strumenti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F795EB-E4CE-4B31-8160-EBC76C526309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D30BE5-90D0-4178-9C86-FB20DECDDE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12156" yWindow="0" windowWidth="29712" windowHeight="16656" firstSheet="1" activeTab="8" xr2:uid="{FC328CB3-F1C2-4520-956D-C4D288DB9EEB}"/>
+    <workbookView xWindow="23412" yWindow="0" windowWidth="24336" windowHeight="16656" firstSheet="1" activeTab="9" xr2:uid="{FC328CB3-F1C2-4520-956D-C4D288DB9EEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Halfling A" sheetId="8" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <sheet name="Fighter A" sheetId="3" r:id="rId6"/>
     <sheet name="Cleric A" sheetId="1" r:id="rId7"/>
     <sheet name="Retro" sheetId="2" r:id="rId8"/>
-    <sheet name="Emporio" sheetId="9" r:id="rId9"/>
+    <sheet name="Arcade" sheetId="9" r:id="rId9"/>
+    <sheet name="Citta" sheetId="11" r:id="rId10"/>
+    <sheet name="Foglio3" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="595">
   <si>
     <t>Giocatore</t>
   </si>
@@ -1212,6 +1214,624 @@
   </si>
   <si>
     <t>by maru</t>
+  </si>
+  <si>
+    <t>--- VILLAGGIO (e superiori) ---</t>
+  </si>
+  <si>
+    <t>Razione (1 giorno)</t>
+  </si>
+  <si>
+    <t>Cibo fresco. Deperisce in 1 settimana.</t>
+  </si>
+  <si>
+    <t>Otre d'acqua</t>
+  </si>
+  <si>
+    <t>1 giorno d'acqua per persona.</t>
+  </si>
+  <si>
+    <t>Trasporta fino a 600 mo di peso.</t>
+  </si>
+  <si>
+    <t>Supporta 150 kg. Arrampicata senza tiro se non sotto stress.</t>
+  </si>
+  <si>
+    <t>Attiva trappole a 10'. Sondare. Due mani.</t>
+  </si>
+  <si>
+    <t>Piccone</t>
+  </si>
+  <si>
+    <t>3 mo</t>
+  </si>
+  <si>
+    <t>Scavare pietra/terra. Come arma: 1d6, due mani.</t>
+  </si>
+  <si>
+    <t>Pala</t>
+  </si>
+  <si>
+    <t>Scavare terra. Come arma improvvisata: 1d4.</t>
+  </si>
+  <si>
+    <t>Luce 30', 1 ora ciascuna. Come arma: 1d4 fuoco.</t>
+  </si>
+  <si>
+    <t>Candele (10)</t>
+  </si>
+  <si>
+    <t>Luce 5', 1 ora ciascuna.</t>
+  </si>
+  <si>
+    <t>Acciarino e pietra focaia</t>
+  </si>
+  <si>
+    <t>Accendere fuoco: 1 round.</t>
+  </si>
+  <si>
+    <t>Piantare chiodi/paletti. Come arma improvvisata: 1d4.</t>
+  </si>
+  <si>
+    <t>Paletti legno (3)</t>
+  </si>
+  <si>
+    <t>Colpo al cuore su vampiro paralizzato: uccide.</t>
+  </si>
+  <si>
+    <t>Gesso (10 pezzi)</t>
+  </si>
+  <si>
+    <t>Segnare percorsi.</t>
+  </si>
+  <si>
+    <t>Simbolo sacro (legno)</t>
+  </si>
+  <si>
+    <t>Necessario per scacciare non-morti.</t>
+  </si>
+  <si>
+    <t>Aglio (testa)</t>
+  </si>
+  <si>
+    <t>Vampiri: TS o non possono avvicinarsi entro 10'.</t>
+  </si>
+  <si>
+    <t>Per fionda. Recuperabili 50% (1-3 su d6).</t>
+  </si>
+  <si>
+    <t>Daga</t>
+  </si>
+  <si>
+    <t>1d4 danni. Lanciabile 10'/20'/30'. Una mano.</t>
+  </si>
+  <si>
+    <t>Ascia</t>
+  </si>
+  <si>
+    <t>1d6 danni. Lanciabile 10'/20'/30'. Una mano.</t>
+  </si>
+  <si>
+    <t>Lancia</t>
+  </si>
+  <si>
+    <t>4 mo</t>
+  </si>
+  <si>
+    <t>1d6 danni. Lanciabile 20'/40'/60'. Una o due mani (1d8).</t>
+  </si>
+  <si>
+    <t>1d4 danni. Due mani. Contundente.</t>
+  </si>
+  <si>
+    <t>1d4 danni. Gittata 40'/80'/160'. Due mani per caricare.</t>
+  </si>
+  <si>
+    <t>Pony</t>
+  </si>
+  <si>
+    <t>40 mo</t>
+  </si>
+  <si>
+    <t>Carico 200 mo. Movimento 40'. Non addestrato al combattimento.</t>
+  </si>
+  <si>
+    <t>Mulo</t>
+  </si>
+  <si>
+    <t>Carico 400 mo. Movimento 40'. Testardo ma resistente.</t>
+  </si>
+  <si>
+    <t>Asino</t>
+  </si>
+  <si>
+    <t>Carico 200 mo. Movimento 40'.</t>
+  </si>
+  <si>
+    <t>Portatore (giorno)</t>
+  </si>
+  <si>
+    <t>Trasporta 100 mo di peso. Morale 6. Non combatte.</t>
+  </si>
+  <si>
+    <t>Guida locale (giorno)</t>
+  </si>
+  <si>
+    <t>Conosce la zona. Morale 7. Non combatte.</t>
+  </si>
+  <si>
+    <t>--- PAESE (e superiori) ---</t>
+  </si>
+  <si>
+    <t>Razione secca (1 settimana)</t>
+  </si>
+  <si>
+    <t>10 mo</t>
+  </si>
+  <si>
+    <t>Cibo conservato. Non deperisce.</t>
+  </si>
+  <si>
+    <t>Zaino</t>
+  </si>
+  <si>
+    <t>Trasporta fino a 400 mo di peso.</t>
+  </si>
+  <si>
+    <t>Rampino</t>
+  </si>
+  <si>
+    <t>Lanciare: TxC vs CA 9. Con corda per scalare.</t>
+  </si>
+  <si>
+    <t>Piede di porco</t>
+  </si>
+  <si>
+    <t>+1 a sfondare porte. Come arma improvvisata: 1d4.</t>
+  </si>
+  <si>
+    <t>Luce 30', 4 ore per fiasca olio. Vento non la spegne.</t>
+  </si>
+  <si>
+    <t>Lanciato 10'/20'/30': TxC vs CA 9. 1d8 fuoco, brucia 2 round (1d8/round).</t>
+  </si>
+  <si>
+    <t>Blocca porta: nemico deve sfondare. Rimuovere: 1 turno (1 round con martello).</t>
+  </si>
+  <si>
+    <t>Borse da sella</t>
+  </si>
+  <si>
+    <t>Per cavalcatura. Capacità 300 mo.</t>
+  </si>
+  <si>
+    <t>Spada corta</t>
+  </si>
+  <si>
+    <t>7 mo</t>
+  </si>
+  <si>
+    <t>1d6 danni. Una mano.</t>
+  </si>
+  <si>
+    <t>1d6 danni. Una mano. Contundente, danni pieni vs scheletri.</t>
+  </si>
+  <si>
+    <t>Arco corto</t>
+  </si>
+  <si>
+    <t>1d6 danni. Gittata 50'/100'/150'. Due mani.</t>
+  </si>
+  <si>
+    <t>Armatura imbottita</t>
+  </si>
+  <si>
+    <t>CA 7 [12].</t>
+  </si>
+  <si>
+    <t>Armatura di cuoio</t>
+  </si>
+  <si>
+    <t>20 mo</t>
+  </si>
+  <si>
+    <t>CA +1. Una mano occupata.</t>
+  </si>
+  <si>
+    <t>Cavallo da sella</t>
+  </si>
+  <si>
+    <t>75 mo</t>
+  </si>
+  <si>
+    <t>Carico 300 mo. Movimento 80'. Non addestrato al combattimento.</t>
+  </si>
+  <si>
+    <t>Cane da guardia</t>
+  </si>
+  <si>
+    <t>DV 1+1, CA 7 [12], morso 1d4. Morale 9. Fiuta intrusi.</t>
+  </si>
+  <si>
+    <t>Sella</t>
+  </si>
+  <si>
+    <t>Necessaria per cavalcare.</t>
+  </si>
+  <si>
+    <t>Carro</t>
+  </si>
+  <si>
+    <t>Carico 1500 mo. Richiede 1-2 animali da tiro.</t>
+  </si>
+  <si>
+    <t>Barca a remi</t>
+  </si>
+  <si>
+    <t>Trasporta 6 persone. Movimento 30'.</t>
+  </si>
+  <si>
+    <t>--- PICCOLA CITTÀ (e superiori) ---</t>
+  </si>
+  <si>
+    <t>Guardare angoli. Riflette sguardo pietrificante: mostro TS Pietrificazione o subisce effetto.</t>
+  </si>
+  <si>
+    <t>Lanciata 10'/20'/30': TxC normale. 1d8 vs non-morti/infernali.</t>
+  </si>
+  <si>
+    <t>Simbolo sacro (argento)</t>
+  </si>
+  <si>
+    <t>Come legno. Più resistente, +1 a Scacciare.</t>
+  </si>
+  <si>
+    <t>Specchio d'argento</t>
+  </si>
+  <si>
+    <t>Vampiri non si riflettono. Utile per identificarli.</t>
+  </si>
+  <si>
+    <t>Quadrelli (20)</t>
+  </si>
+  <si>
+    <t>Per balestra. Recuperabili 50% (1-3 su d6).</t>
+  </si>
+  <si>
+    <t>Spada lunga</t>
+  </si>
+  <si>
+    <t>1d8 danni. Una mano.</t>
+  </si>
+  <si>
+    <t>Ascia da battaglia</t>
+  </si>
+  <si>
+    <t>1d8 danni. Una mano. Può essere usata a due mani.</t>
+  </si>
+  <si>
+    <t>Martello da guerra</t>
+  </si>
+  <si>
+    <t>1d8 danni. Gittata 70'/140'/210'. Due mani.</t>
+  </si>
+  <si>
+    <t>Balestra leggera</t>
+  </si>
+  <si>
+    <t>1d6 danni. Gittata 60'/120'/180'. Due mani. Ricarica 1 round.</t>
+  </si>
+  <si>
+    <t>Armatura borchiata</t>
+  </si>
+  <si>
+    <t>CA 6 [13].</t>
+  </si>
+  <si>
+    <t>Cotta di maglia</t>
+  </si>
+  <si>
+    <t>CA 5 [14].</t>
+  </si>
+  <si>
+    <t>Elmo</t>
+  </si>
+  <si>
+    <t>Protegge da colpi critici alla testa (opzionale).</t>
+  </si>
+  <si>
+    <t>Mercenario (giorno)</t>
+  </si>
+  <si>
+    <t>Guerriero liv.1. DV 1, CA 6 [13], spada 1d8. Morale 8.</t>
+  </si>
+  <si>
+    <t>Pozione Cura Ferite Leggere</t>
+  </si>
+  <si>
+    <t>Cura 1d6+1 HP. Bere: 1 azione.</t>
+  </si>
+  <si>
+    <t>Pozione Neutralizza Veleno</t>
+  </si>
+  <si>
+    <t>Rimuove qualsiasi veleno immediatamente. Consigliata.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. 1d6+1 danni. Colpo automatico. Gittata 150'.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. CA 2 vs distanza, CA 4 vs mischia. Durata 2 turni.</t>
+  </si>
+  <si>
+    <t>Pergamena: Sonno</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. 2d8 DV si addormentano. Gittata 240'. No TS.</t>
+  </si>
+  <si>
+    <t>Pergamena: Charme</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. 1 bersaglio ti considera amico. TS nega.</t>
+  </si>
+  <si>
+    <t>Pergamena: Individuazione Magia</t>
+  </si>
+  <si>
+    <t>Mago/Elfo/Chierico. Rileva magia entro 60'. Durata 2 turni.</t>
+  </si>
+  <si>
+    <t>Mago/Elfo/Chierico. Luce 15'. Su occhi: TS o accecato (-4 TxC). Durata 12 turni.</t>
+  </si>
+  <si>
+    <t>Mago/Elfo/Chierico. Malvagi -1 TxC, +1 TS. Evocati non toccano. Durata 12 turni.</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Cura 1d6+1 HP. Tocco. Alternativa: 1d6+1 danni a non-morti (TxC).</t>
+  </si>
+  <si>
+    <t>--- MEDIA/GRANDE CITTÀ ---</t>
+  </si>
+  <si>
+    <t>Spada a due mani</t>
+  </si>
+  <si>
+    <t>1d10 danni. Due mani. Attacca per ultimo.</t>
+  </si>
+  <si>
+    <t>Alabarda</t>
+  </si>
+  <si>
+    <t>Balestra pesante</t>
+  </si>
+  <si>
+    <t>1d8 danni. Gittata 80'/160'/240'. Due mani. Ricarica 2 round.</t>
+  </si>
+  <si>
+    <t>Armatura a scaglie</t>
+  </si>
+  <si>
+    <t>45 mo</t>
+  </si>
+  <si>
+    <t>CA 4 [15].</t>
+  </si>
+  <si>
+    <t>Armatura a bande</t>
+  </si>
+  <si>
+    <t>90 mo</t>
+  </si>
+  <si>
+    <t>CA 3 [16].</t>
+  </si>
+  <si>
+    <t>Cavallo da guerra</t>
+  </si>
+  <si>
+    <t>Carico 400 mo. Movimento 60'. Attacca: 2 zoccoli 1d6. Morale 9.</t>
+  </si>
+  <si>
+    <t>Guardia del corpo (giorno)</t>
+  </si>
+  <si>
+    <t>Guerriero liv.2. DV 2, CA 4 [15], spada 1d8. Morale 9.</t>
+  </si>
+  <si>
+    <t>Pozione Cura Ferite Gravi</t>
+  </si>
+  <si>
+    <t>600 mo</t>
+  </si>
+  <si>
+    <t>Cura 2d6+2 HP. Bere: 1 azione.</t>
+  </si>
+  <si>
+    <t>Durata 1 turno. Movimento x2, 2 attacchi/round. Non cumulabile.</t>
+  </si>
+  <si>
+    <t>500 mo</t>
+  </si>
+  <si>
+    <t>Durata: fino a interruzione. Termina se attacchi/lanci incantesimo.</t>
+  </si>
+  <si>
+    <t>Pozione Resistenza Fuoco</t>
+  </si>
+  <si>
+    <t>Durata 1 turno. Immune danni fuoco normali. +2 TS vs fuoco magico.</t>
+  </si>
+  <si>
+    <t>Durata 1 turno. FOR 18 (+3 TxC/danni mischia).</t>
+  </si>
+  <si>
+    <t>Durata 6 turni. Solo verticale 6'/round. No movimento orizzontale autonomo.</t>
+  </si>
+  <si>
+    <t>Pozione Forma Gassosa</t>
+  </si>
+  <si>
+    <t>450 mo</t>
+  </si>
+  <si>
+    <t>Durata 1 turno. Passa attraverso fessure. Immune attacchi fisici. No attaccare.</t>
+  </si>
+  <si>
+    <t>Pozione Eroismo</t>
+  </si>
+  <si>
+    <t>350 mo</t>
+  </si>
+  <si>
+    <t>Solo Guerrieri. Durata 1 turno. +1d4 HP temporanei, +2 TxC.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Bersaglio invisibile. Termina se attacca. Nemici -4 TxC.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Area 10'x10'x10'. TS o intrappolato. Fuoco brucia in 2 round (1d6 danni).</t>
+  </si>
+  <si>
+    <t>Pergamena: Levitazione</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Solo verticale. Durata 6 turni +1/livello.</t>
+  </si>
+  <si>
+    <t>Pergamena: Bussare</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Apre una porta chiusa/bloccata/magica.</t>
+  </si>
+  <si>
+    <t>Pergamena: Rimuovi Paralisi</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Rimuove paralisi da 1d4 creature. Consigliata.</t>
+  </si>
+  <si>
+    <t>Pergamena: Dissolvi Magie</t>
+  </si>
+  <si>
+    <t>Mago/Elfo/Chierico. Rimuove effetti magici. Gittata 120'. Consigliata.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. 1d6/livello fuoco (max 10d6). TS dimezza. Raggio 20'. Gittata 240'.</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. 1d6/livello (max 10d6). TS dimezza. Linea 60'x5'. Rimbalza.</t>
+  </si>
+  <si>
+    <t>Pergamena: Blocca Persone</t>
+  </si>
+  <si>
+    <t>Mago/Elfo/Chierico. Paralizza 1d4 umanoidi. TS nega. Durata 1 turno +1/livello.</t>
+  </si>
+  <si>
+    <t>--- RARO (richiede ricerca o contatti) ---</t>
+  </si>
+  <si>
+    <t>Spada corta +1</t>
+  </si>
+  <si>
+    <t>1500 mo</t>
+  </si>
+  <si>
+    <t>1d6+1 danni. +1 TxC. Una mano.</t>
+  </si>
+  <si>
+    <t>Spada lunga +1</t>
+  </si>
+  <si>
+    <t>2000 mo</t>
+  </si>
+  <si>
+    <t>1d8+1 danni. +1 TxC. Una mano.</t>
+  </si>
+  <si>
+    <t>Mazza +1</t>
+  </si>
+  <si>
+    <t>1d6+1 danni. +1 TxC. Contundente, danni pieni vs scheletri.</t>
+  </si>
+  <si>
+    <t>Martello da guerra +1</t>
+  </si>
+  <si>
+    <t>Daga +1</t>
+  </si>
+  <si>
+    <t>1000 mo</t>
+  </si>
+  <si>
+    <t>1d4+1 danni. +1 TxC. Lanciabile 10'/20'/30'.</t>
+  </si>
+  <si>
+    <t>Arco corto +1</t>
+  </si>
+  <si>
+    <t>3000 mo</t>
+  </si>
+  <si>
+    <t>1d6+1 danni. +1 TxC. Gittata 50'/100'/150'. Due mani.</t>
+  </si>
+  <si>
+    <t>Frecce +1 (10)</t>
+  </si>
+  <si>
+    <t>+1 TxC e danni. Non recuperabili.</t>
+  </si>
+  <si>
+    <t>Armatura di cuoio +1</t>
+  </si>
+  <si>
+    <t>Cotta di maglia +1</t>
+  </si>
+  <si>
+    <t>3500 mo</t>
+  </si>
+  <si>
+    <t>Scudo +1</t>
+  </si>
+  <si>
+    <t>CA +2 totale. Una mano occupata.</t>
+  </si>
+  <si>
+    <t>Anello Protezione +1</t>
+  </si>
+  <si>
+    <t>5000 mo</t>
+  </si>
+  <si>
+    <t>+1 CA e +1 tutti i TS. Non cumulabile con armatura magica.</t>
+  </si>
+  <si>
+    <t>Stivali Elfici</t>
+  </si>
+  <si>
+    <t>Movimento silenzioso. Sorpresa 1-4 su d6.</t>
+  </si>
+  <si>
+    <t>Mantello Elfico</t>
+  </si>
+  <si>
+    <t>Quasi invisibile se immobile. Sorpresa 1-4 su d6 (1-5 con stivali).</t>
+  </si>
+  <si>
+    <t>Corda Arrampicata</t>
+  </si>
+  <si>
+    <t>15m. Si arrampica su comando. Regge 500 kg.</t>
+  </si>
+  <si>
+    <t>Borsa Conservante</t>
+  </si>
+  <si>
+    <t>2500 mo</t>
+  </si>
+  <si>
+    <t>Contiene 500 mo di peso, pesa sempre 5 mo.</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +2549,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2429,23 +3049,86 @@
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2465,11 +3148,44 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2491,115 +3207,6 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2676,13 +3283,32 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2714,32 +3340,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color theme="1"/>
         <name val="Aptos"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9335,11 +9942,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CFC2B8A-D537-42C2-9576-BDC96890C46F}" name="Tabella1" displayName="Tabella1" ref="A1:E40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CFC2B8A-D537-42C2-9576-BDC96890C46F}" name="Tabella1" displayName="Tabella1" ref="A1:E40" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BE96BCF5-334D-4F20-8722-3145ABDC81EA}" name="Oggetto" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{23DBEE6D-E19E-482F-A20A-3F3284C9D84B}" name="Qt." dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{CE44C6FC-0DBC-4316-AC79-C083711A35A2}" name="Costo" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{BE96BCF5-334D-4F20-8722-3145ABDC81EA}" name="Oggetto" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{23DBEE6D-E19E-482F-A20A-3F3284C9D84B}" name="Qt." dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{CE44C6FC-0DBC-4316-AC79-C083711A35A2}" name="Costo" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{13F2738A-AAED-4162-A6FC-D1A5B56EBD56}" name="Slot" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{C208413F-8AA4-49BE-A972-17EB9781744E}" name="Note" dataDxfId="0"/>
   </tableColumns>
@@ -9807,24 +10414,24 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>1</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>6</v>
       </c>
@@ -9836,24 +10443,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>1</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>7</v>
       </c>
@@ -9865,24 +10472,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>0</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>8</v>
       </c>
@@ -9894,24 +10501,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>1</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>10</v>
       </c>
@@ -9923,24 +10530,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>0</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>10</v>
       </c>
@@ -9952,15 +10559,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
@@ -10003,10 +10610,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -10031,8 +10638,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -10059,8 +10666,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -10172,11 +10779,11 @@
         <v>238</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="N20" s="177" t="s">
+      <c r="N20" s="200" t="s">
         <v>179</v>
       </c>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -10427,10 +11034,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -10482,10 +11089,10 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>200</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="P38" s="57"/>
     </row>
     <row r="39" spans="1:27" ht="18" x14ac:dyDescent="0.3">
@@ -10534,10 +11141,10 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>176</v>
       </c>
-      <c r="N39" s="181"/>
+      <c r="N39" s="204"/>
       <c r="O39" s="3" t="s">
         <v>118</v>
       </c>
@@ -10590,10 +11197,10 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78" t="s">
         <v>201</v>
       </c>
@@ -10601,26 +11208,2030 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5B8450-D323-4BD0-AC14-7E0806B219F9}">
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.5546875" style="166" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="165" customWidth="1"/>
+    <col min="3" max="3" width="9" style="165" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="165" customWidth="1"/>
+    <col min="5" max="5" width="52.21875" style="164" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="164"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="168"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="225" t="s">
+        <v>356</v>
+      </c>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F25" s="173" t="s">
+        <v>357</v>
+      </c>
+      <c r="G25" s="174"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="174"/>
+      <c r="M25" s="174"/>
+      <c r="N25" s="174"/>
+      <c r="O25" s="174"/>
+      <c r="P25" s="175" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A26" s="169"/>
+      <c r="B26" s="170"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="170"/>
+      <c r="E26" s="172"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="171"/>
+      <c r="B36" s="171"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
+      <c r="E36" s="171"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="166"/>
+      <c r="C37" s="166"/>
+      <c r="D37" s="166"/>
+      <c r="E37" s="166"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="171"/>
+      <c r="B38" s="171"/>
+      <c r="C38" s="171"/>
+      <c r="D38" s="171"/>
+      <c r="E38" s="171"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="166"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="171"/>
+      <c r="B40" s="171"/>
+      <c r="C40" s="171"/>
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68D513C-AAB4-45B3-A236-E57180D92C9F}">
+  <dimension ref="A1:E115"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>398</v>
+      </c>
+      <c r="D12" t="s">
+        <v>329</v>
+      </c>
+      <c r="E12" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>268</v>
+      </c>
+      <c r="D15" t="s">
+        <v>329</v>
+      </c>
+      <c r="E15" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>412</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" t="s">
+        <v>329</v>
+      </c>
+      <c r="E16" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>417</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>422</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>268</v>
+      </c>
+      <c r="D23" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>426</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>427</v>
+      </c>
+      <c r="D24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E24" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>429</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" t="s">
+        <v>329</v>
+      </c>
+      <c r="E25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>431</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>433</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" t="s">
+        <v>329</v>
+      </c>
+      <c r="E27" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>270</v>
+      </c>
+      <c r="D28" t="s">
+        <v>329</v>
+      </c>
+      <c r="E28" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>438</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>439</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>441</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>270</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>443</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>270</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>272</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>269</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>439</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>273</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>450</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>439</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>279</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>453</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>270</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>456</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>458</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>314</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>460</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>212</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>439</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>463</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>464</v>
+      </c>
+      <c r="D45" t="s">
+        <v>329</v>
+      </c>
+      <c r="E45" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>466</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>313</v>
+      </c>
+      <c r="D46" t="s">
+        <v>329</v>
+      </c>
+      <c r="E46" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>468</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>313</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>470</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>295</v>
+      </c>
+      <c r="D48" t="s">
+        <v>329</v>
+      </c>
+      <c r="E48" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>472</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>292</v>
+      </c>
+      <c r="D49" t="s">
+        <v>329</v>
+      </c>
+      <c r="E49" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>271</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>270</v>
+      </c>
+      <c r="D51" t="s">
+        <v>329</v>
+      </c>
+      <c r="E51" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>313</v>
+      </c>
+      <c r="D52" t="s">
+        <v>329</v>
+      </c>
+      <c r="E52" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" t="s">
+        <v>329</v>
+      </c>
+      <c r="E53" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>479</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>315</v>
+      </c>
+      <c r="D54" t="s">
+        <v>329</v>
+      </c>
+      <c r="E54" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>481</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>270</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>483</v>
+      </c>
+      <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>439</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>485</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>453</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>487</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>453</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>427</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>489</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>315</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>491</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>315</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>493</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>427</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>495</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>439</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>497</v>
+      </c>
+      <c r="B64">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>272</v>
+      </c>
+      <c r="D64" t="s">
+        <v>329</v>
+      </c>
+      <c r="E64" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>499</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>285</v>
+      </c>
+      <c r="D65" t="s">
+        <v>329</v>
+      </c>
+      <c r="E65" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>501</v>
+      </c>
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>283</v>
+      </c>
+      <c r="D66" t="s">
+        <v>329</v>
+      </c>
+      <c r="E66" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>291</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>295</v>
+      </c>
+      <c r="D67" t="s">
+        <v>329</v>
+      </c>
+      <c r="E67" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>295</v>
+      </c>
+      <c r="D68" t="s">
+        <v>329</v>
+      </c>
+      <c r="E68" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>505</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" t="s">
+        <v>329</v>
+      </c>
+      <c r="E69" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>507</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>295</v>
+      </c>
+      <c r="D70" t="s">
+        <v>329</v>
+      </c>
+      <c r="E70" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>509</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>295</v>
+      </c>
+      <c r="D71" t="s">
+        <v>329</v>
+      </c>
+      <c r="E71" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>301</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>292</v>
+      </c>
+      <c r="D72" t="s">
+        <v>329</v>
+      </c>
+      <c r="E72" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>300</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" t="s">
+        <v>329</v>
+      </c>
+      <c r="E73" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>295</v>
+      </c>
+      <c r="D74" t="s">
+        <v>329</v>
+      </c>
+      <c r="E74" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>515</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>314</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>517</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>453</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>518</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>292</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>520</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>521</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>523</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>524</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>526</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>287</v>
+      </c>
+      <c r="D81" t="s">
+        <v>329</v>
+      </c>
+      <c r="E81" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>528</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82" t="s">
+        <v>398</v>
+      </c>
+      <c r="D82" t="s">
+        <v>329</v>
+      </c>
+      <c r="E82" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>530</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>531</v>
+      </c>
+      <c r="D83" t="s">
+        <v>329</v>
+      </c>
+      <c r="E83" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>286</v>
+      </c>
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84" t="s">
+        <v>308</v>
+      </c>
+      <c r="D84" t="s">
+        <v>329</v>
+      </c>
+      <c r="E84" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>288</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>534</v>
+      </c>
+      <c r="D85" t="s">
+        <v>329</v>
+      </c>
+      <c r="E85" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>536</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86" t="s">
+        <v>308</v>
+      </c>
+      <c r="D86" t="s">
+        <v>329</v>
+      </c>
+      <c r="E86" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>306</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>534</v>
+      </c>
+      <c r="D87" t="s">
+        <v>329</v>
+      </c>
+      <c r="E87" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88" t="s">
+        <v>308</v>
+      </c>
+      <c r="D88" t="s">
+        <v>329</v>
+      </c>
+      <c r="E88" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>540</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>541</v>
+      </c>
+      <c r="D89" t="s">
+        <v>329</v>
+      </c>
+      <c r="E89" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>543</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90" t="s">
+        <v>544</v>
+      </c>
+      <c r="D90" t="s">
+        <v>329</v>
+      </c>
+      <c r="E90" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>294</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" t="s">
+        <v>329</v>
+      </c>
+      <c r="E91" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>296</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92" t="s">
+        <v>289</v>
+      </c>
+      <c r="D92" t="s">
+        <v>329</v>
+      </c>
+      <c r="E92" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>548</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>289</v>
+      </c>
+      <c r="D93" t="s">
+        <v>329</v>
+      </c>
+      <c r="E93" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>550</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+      <c r="C94" t="s">
+        <v>289</v>
+      </c>
+      <c r="D94" t="s">
+        <v>329</v>
+      </c>
+      <c r="E94" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>552</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>289</v>
+      </c>
+      <c r="D95" t="s">
+        <v>329</v>
+      </c>
+      <c r="E95" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>554</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>308</v>
+      </c>
+      <c r="D96" t="s">
+        <v>329</v>
+      </c>
+      <c r="E96" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>297</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97" t="s">
+        <v>308</v>
+      </c>
+      <c r="D97" t="s">
+        <v>329</v>
+      </c>
+      <c r="E97" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>298</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98" t="s">
+        <v>308</v>
+      </c>
+      <c r="D98" t="s">
+        <v>329</v>
+      </c>
+      <c r="E98" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>558</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>308</v>
+      </c>
+      <c r="D99" t="s">
+        <v>329</v>
+      </c>
+      <c r="E99" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>561</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101" t="s">
+        <v>562</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>564</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102" t="s">
+        <v>565</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>567</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>562</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>569</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>565</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+      <c r="E104" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>570</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105" t="s">
+        <v>571</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>573</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>574</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>576</v>
+      </c>
+      <c r="B107">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>534</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>578</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>565</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>579</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>580</v>
+      </c>
+      <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>581</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>562</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>583</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>584</v>
+      </c>
+      <c r="D111" t="s">
+        <v>329</v>
+      </c>
+      <c r="E111" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>586</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>574</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>588</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>574</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>590</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>565</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>592</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>593</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115" t="s">
+        <v>594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10769,24 +13380,24 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>2</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>371</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>10</v>
       </c>
@@ -10798,24 +13409,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>0</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>11</v>
       </c>
@@ -10827,24 +13438,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>1</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>11</v>
       </c>
@@ -10856,24 +13467,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>2</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>13</v>
       </c>
@@ -10885,24 +13496,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>0</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>12</v>
       </c>
@@ -10914,15 +13525,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
@@ -10965,10 +13576,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -10993,8 +13604,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -11021,8 +13632,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -11134,11 +13745,11 @@
         <v>238</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="N20" s="177" t="s">
+      <c r="N20" s="200" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -11407,10 +14018,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -11462,10 +14073,10 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>186</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="P38" s="57"/>
     </row>
     <row r="39" spans="1:27" ht="18" x14ac:dyDescent="0.3">
@@ -11514,11 +14125,13 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="N39" s="181"/>
-      <c r="O39" s="3"/>
+      <c r="N39" s="204"/>
+      <c r="O39" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="P39" s="57"/>
       <c r="AA39"/>
     </row>
@@ -11568,32 +14181,32 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78"/>
       <c r="P40" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -11745,27 +14358,27 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>1</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="L6" s="211" t="s">
+      <c r="L6" s="183" t="s">
         <v>372</v>
       </c>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>371</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>6</v>
       </c>
@@ -11777,24 +14390,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>0</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>6</v>
       </c>
@@ -11806,24 +14419,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>2</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>7</v>
       </c>
@@ -11835,24 +14448,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>0</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>10</v>
       </c>
@@ -11864,24 +14477,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>171</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>1</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>9</v>
       </c>
@@ -11893,15 +14506,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
@@ -11944,10 +14557,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -11972,8 +14585,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -11999,8 +14612,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -12109,11 +14722,11 @@
         <v>238</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="N20" s="177" t="s">
+      <c r="N20" s="200" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -12381,10 +14994,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -12436,10 +15049,10 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>174</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="O38" s="2" t="s">
         <v>177</v>
       </c>
@@ -12491,10 +15104,10 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>176</v>
       </c>
-      <c r="N39" s="181"/>
+      <c r="N39" s="204"/>
       <c r="O39" s="3" t="s">
         <v>118</v>
       </c>
@@ -12547,10 +15160,10 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78" t="s">
         <v>119</v>
       </c>
@@ -12558,23 +15171,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -12726,27 +15339,27 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>0</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="L6" s="211" t="s">
+      <c r="L6" s="183" t="s">
         <v>373</v>
       </c>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>12</v>
       </c>
@@ -12758,24 +15371,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>2</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>14</v>
       </c>
@@ -12787,24 +15400,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>1</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>12</v>
       </c>
@@ -12816,24 +15429,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>1</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>16</v>
       </c>
@@ -12845,24 +15458,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>-1</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>14</v>
       </c>
@@ -12874,15 +15487,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
@@ -12925,10 +15538,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -12953,8 +15566,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -12981,8 +15594,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -13094,11 +15707,11 @@
         <v>238</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="N20" s="177" t="s">
+      <c r="N20" s="200" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:21" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -13393,10 +16006,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -13448,10 +16061,10 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>82</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="P38" s="57"/>
     </row>
     <row r="39" spans="1:27" ht="18" x14ac:dyDescent="0.3">
@@ -13500,10 +16113,10 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>84</v>
       </c>
-      <c r="N39" s="181"/>
+      <c r="N39" s="204"/>
       <c r="O39" s="3" t="s">
         <v>118</v>
       </c>
@@ -13556,10 +16169,10 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78" t="s">
         <v>119</v>
       </c>
@@ -13567,23 +16180,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -13735,24 +16348,24 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>-1</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>13</v>
       </c>
@@ -13764,24 +16377,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>0</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>14</v>
       </c>
@@ -13793,24 +16406,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>1</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>13</v>
       </c>
@@ -13822,24 +16435,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>2</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>16</v>
       </c>
@@ -13851,24 +16464,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>0</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>15</v>
       </c>
@@ -13880,15 +16493,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>-1</v>
       </c>
@@ -13931,10 +16544,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -13959,8 +16572,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -13987,8 +16600,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -14094,9 +16707,9 @@
         <v>238</v>
       </c>
       <c r="B20" s="37"/>
-      <c r="N20" s="177"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="N20" s="200"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -14360,10 +16973,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -14415,10 +17028,10 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>139</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="P38" s="57"/>
     </row>
     <row r="39" spans="1:27" ht="18" x14ac:dyDescent="0.3">
@@ -14467,11 +17080,13 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>139</v>
       </c>
-      <c r="N39" s="181"/>
-      <c r="O39" s="3"/>
+      <c r="N39" s="204"/>
+      <c r="O39" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="P39" s="57"/>
       <c r="AA39"/>
     </row>
@@ -14521,32 +17136,32 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78"/>
       <c r="P40" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -14699,27 +17314,27 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>2</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="L6" s="211" t="s">
+      <c r="L6" s="183" t="s">
         <v>374</v>
       </c>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>371</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>10</v>
       </c>
@@ -14731,24 +17346,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>1</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>13</v>
       </c>
@@ -14760,24 +17375,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>0</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>14</v>
       </c>
@@ -14789,24 +17404,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>-1</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>13</v>
       </c>
@@ -14818,24 +17433,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>-2</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>16</v>
       </c>
@@ -14847,15 +17462,15 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
@@ -14898,10 +17513,10 @@
       <c r="P13" s="60"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="E14" s="123" t="s">
         <v>21</v>
       </c>
@@ -14926,8 +17541,8 @@
       <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="E15" s="126" t="s">
         <v>37</v>
       </c>
@@ -14953,8 +17568,8 @@
       <c r="P15" s="52"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="E16" s="123" t="s">
         <v>18</v>
       </c>
@@ -15064,11 +17679,11 @@
       </c>
       <c r="B20" s="37"/>
       <c r="E20" s="133"/>
-      <c r="N20" s="177" t="s">
+      <c r="N20" s="200" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="177"/>
-      <c r="P20" s="178"/>
+      <c r="O20" s="200"/>
+      <c r="P20" s="201"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
@@ -15335,10 +17950,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -15390,10 +18005,10 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>107</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="O38" s="2" t="s">
         <v>111</v>
       </c>
@@ -15445,10 +18060,10 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="N39" s="181"/>
+      <c r="N39" s="204"/>
       <c r="O39" s="3" t="s">
         <v>118</v>
       </c>
@@ -15501,10 +18116,10 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="78" t="s">
         <v>119</v>
       </c>
@@ -15512,11 +18127,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="N20:P20"/>
     <mergeCell ref="A14:B16"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="M6:O6"/>
@@ -15529,6 +18139,11 @@
     <mergeCell ref="C10:I10"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="C11:I11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="N20:P20"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -15680,27 +18295,27 @@
       <c r="B6" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="206" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
       <c r="J6" s="122">
         <v>0</v>
       </c>
       <c r="K6" s="122"/>
-      <c r="L6" s="211" t="s">
+      <c r="L6" s="183" t="s">
         <v>372</v>
       </c>
-      <c r="M6" s="176" t="s">
+      <c r="M6" s="207" t="s">
         <v>371</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="56">
         <v>9</v>
       </c>
@@ -15712,24 +18327,24 @@
       <c r="B7" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="206"/>
       <c r="J7" s="122">
         <v>-1</v>
       </c>
       <c r="K7" s="122"/>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
       <c r="P7" s="56">
         <v>9</v>
       </c>
@@ -15741,24 +18356,24 @@
       <c r="B8" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
+      <c r="D8" s="206"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="206"/>
       <c r="J8" s="122">
         <v>0</v>
       </c>
       <c r="K8" s="122"/>
-      <c r="M8" s="176" t="s">
+      <c r="M8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
       <c r="P8" s="56">
         <v>11</v>
       </c>
@@ -15770,24 +18385,24 @@
       <c r="B9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="206" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
       <c r="J9" s="122">
         <v>-1</v>
       </c>
       <c r="K9" s="122"/>
-      <c r="M9" s="176" t="s">
+      <c r="M9" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="176"/>
-      <c r="O9" s="176"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
       <c r="P9" s="56">
         <v>14</v>
       </c>
@@ -15799,24 +18414,24 @@
       <c r="B10" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="206" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="206"/>
       <c r="J10" s="122">
         <v>1</v>
       </c>
       <c r="K10" s="122"/>
-      <c r="M10" s="176" t="s">
+      <c r="M10" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
       <c r="P10" s="56">
         <v>11</v>
       </c>
@@ -15828,25 +18443,25 @@
       <c r="B11" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
       <c r="J11" s="122">
         <v>0</v>
       </c>
       <c r="K11" s="122"/>
-      <c r="M11" s="204" t="s">
+      <c r="M11" s="214" t="s">
         <v>366</v>
       </c>
-      <c r="N11" s="204"/>
-      <c r="O11" s="204"/>
-      <c r="P11" s="205"/>
+      <c r="N11" s="214"/>
+      <c r="O11" s="214"/>
+      <c r="P11" s="215"/>
     </row>
     <row r="12" spans="1:16" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="58"/>
@@ -15864,19 +18479,19 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="123"/>
-      <c r="H13" s="206" t="s">
+      <c r="H13" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="206" t="s">
+      <c r="I13" s="179" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="206" t="s">
+      <c r="J13" s="179" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="208" t="s">
+      <c r="K13" s="180" t="s">
         <v>369</v>
       </c>
-      <c r="L13" s="206" t="s">
+      <c r="L13" s="179" t="s">
         <v>367</v>
       </c>
       <c r="N13" s="34" t="s">
@@ -15886,10 +18501,10 @@
       <c r="P13" s="84"/>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="209"/>
       <c r="D14" s="123" t="s">
         <v>21</v>
       </c>
@@ -15908,10 +18523,10 @@
         <f>H14/5</f>
         <v>4</v>
       </c>
-      <c r="K14" s="208" t="s">
+      <c r="K14" s="180" t="s">
         <v>370</v>
       </c>
-      <c r="L14" s="206" t="s">
+      <c r="L14" s="179" t="s">
         <v>47</v>
       </c>
       <c r="N14" s="20" t="s">
@@ -15921,8 +18536,8 @@
       <c r="P14" s="85"/>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
       <c r="D15" s="126" t="s">
         <v>37</v>
       </c>
@@ -15942,10 +18557,10 @@
         <f t="shared" ref="J15:J18" si="0">H15/5</f>
         <v>12</v>
       </c>
-      <c r="K15" s="209" t="s">
+      <c r="K15" s="181" t="s">
         <v>47</v>
       </c>
-      <c r="L15" s="210" t="s">
+      <c r="L15" s="182" t="s">
         <v>47</v>
       </c>
       <c r="N15" s="20" t="s">
@@ -15955,8 +18570,8 @@
       <c r="P15" s="85"/>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
       <c r="D16" s="123" t="s">
         <v>18</v>
       </c>
@@ -15975,11 +18590,11 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K16" s="208">
+      <c r="K16" s="180">
         <f>J16+(J16/2)</f>
         <v>18</v>
       </c>
-      <c r="L16" s="207" t="s">
+      <c r="L16" s="216" t="s">
         <v>368</v>
       </c>
       <c r="N16" s="20" t="s">
@@ -16012,11 +18627,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K17" s="209">
+      <c r="K17" s="181">
         <f t="shared" ref="K17:K18" si="1">J17+(J17/2)</f>
         <v>3</v>
       </c>
-      <c r="L17" s="207"/>
+      <c r="L17" s="216"/>
       <c r="N17" s="20" t="s">
         <v>60</v>
       </c>
@@ -16046,11 +18661,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K18" s="208">
+      <c r="K18" s="180">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L18" s="207"/>
+      <c r="L18" s="216"/>
       <c r="N18" s="20" t="s">
         <v>61</v>
       </c>
@@ -16075,10 +18690,10 @@
         <v>69</v>
       </c>
       <c r="J19" s="132"/>
-      <c r="K19" s="209" t="s">
+      <c r="K19" s="181" t="s">
         <v>47</v>
       </c>
-      <c r="L19" s="210" t="s">
+      <c r="L19" s="182" t="s">
         <v>47</v>
       </c>
       <c r="N19" s="20" t="s">
@@ -16092,11 +18707,11 @@
         <v>238</v>
       </c>
       <c r="B20" s="87"/>
-      <c r="N20" s="183" t="s">
+      <c r="N20" s="212" t="s">
         <v>62</v>
       </c>
-      <c r="O20" s="183"/>
-      <c r="P20" s="184"/>
+      <c r="O20" s="212"/>
+      <c r="P20" s="213"/>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89" t="s">
@@ -16360,10 +18975,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M37" s="179" t="s">
+      <c r="M37" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="179"/>
+      <c r="N37" s="202"/>
       <c r="O37" s="24" t="s">
         <v>27</v>
       </c>
@@ -16415,10 +19030,10 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="M38" s="180" t="s">
+      <c r="M38" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="N38" s="180"/>
+      <c r="N38" s="203"/>
       <c r="P38" s="57"/>
     </row>
     <row r="39" spans="1:27" ht="18" x14ac:dyDescent="0.3">
@@ -16467,10 +19082,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="M39" s="181" t="s">
+      <c r="M39" s="204" t="s">
         <v>84</v>
       </c>
-      <c r="N39" s="181"/>
+      <c r="N39" s="204"/>
       <c r="O39" s="3" t="s">
         <v>83</v>
       </c>
@@ -16523,10 +19138,10 @@
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="M40" s="182" t="s">
+      <c r="M40" s="205" t="s">
         <v>82</v>
       </c>
-      <c r="N40" s="182"/>
+      <c r="N40" s="205"/>
       <c r="O40" s="143" t="s">
         <v>221</v>
       </c>
@@ -16534,6 +19149,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="N20:P20"/>
@@ -16542,17 +19168,6 @@
     <mergeCell ref="M38:N38"/>
     <mergeCell ref="M11:P11"/>
     <mergeCell ref="L16:L18"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
@@ -16608,16 +19223,16 @@
       <c r="I2" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="198" t="s">
+      <c r="J2" s="217" t="s">
         <v>387</v>
       </c>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="198"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="198"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="217"/>
+      <c r="M2" s="217"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="217"/>
+      <c r="P2" s="218"/>
+      <c r="Q2" s="217"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -16635,16 +19250,16 @@
       <c r="G3" s="2"/>
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
-      <c r="J3" s="200" t="s">
+      <c r="J3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="201"/>
-      <c r="L3" s="201"/>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
-      <c r="Q3" s="201"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="176"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
     </row>
     <row r="4" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="151">
@@ -16659,14 +19274,14 @@
       <c r="G4" s="145"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="M4" s="201"/>
-      <c r="N4" s="201"/>
-      <c r="O4" s="201"/>
-      <c r="P4" s="201"/>
-      <c r="Q4" s="201"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="176"/>
+      <c r="N4" s="176"/>
+      <c r="O4" s="176"/>
+      <c r="P4" s="176"/>
+      <c r="Q4" s="176"/>
     </row>
     <row r="5" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="124">
@@ -16681,14 +19296,14 @@
       <c r="G5" s="2"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="201"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="176"/>
+      <c r="Q5" s="176"/>
     </row>
     <row r="6" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="151">
@@ -16703,16 +19318,16 @@
       <c r="G6" s="145"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="203" t="s">
+      <c r="J6" s="178" t="s">
         <v>360</v>
       </c>
-      <c r="K6" s="200"/>
-      <c r="L6" s="200"/>
-      <c r="M6" s="200"/>
-      <c r="N6" s="200"/>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
-      <c r="Q6" s="200"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="124">
@@ -16727,26 +19342,26 @@
       <c r="G7" s="2"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
-      <c r="J7" s="225" t="s">
+      <c r="J7" s="194" t="s">
         <v>381</v>
       </c>
-      <c r="K7" s="212" t="s">
+      <c r="K7" s="184" t="s">
         <v>375</v>
       </c>
-      <c r="L7" s="212" t="s">
+      <c r="L7" s="184" t="s">
         <v>376</v>
       </c>
-      <c r="M7" s="212" t="s">
+      <c r="M7" s="184" t="s">
         <v>377</v>
       </c>
-      <c r="N7" s="212" t="s">
+      <c r="N7" s="184" t="s">
         <v>378</v>
       </c>
-      <c r="O7" s="212" t="s">
+      <c r="O7" s="184" t="s">
         <v>379</v>
       </c>
-      <c r="P7" s="212"/>
-      <c r="Q7" s="212"/>
+      <c r="P7" s="184"/>
+      <c r="Q7" s="184"/>
     </row>
     <row r="8" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="151">
@@ -16761,16 +19376,16 @@
       <c r="G8" s="145"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="200" t="s">
+      <c r="J8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="200"/>
-      <c r="L8" s="200"/>
-      <c r="M8" s="200"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
-      <c r="Q8" s="200"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
     </row>
     <row r="9" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="124">
@@ -16785,16 +19400,16 @@
       <c r="G9" s="2"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="200" t="s">
+      <c r="J9" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="K9" s="200"/>
-      <c r="L9" s="200"/>
-      <c r="M9" s="200"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
-      <c r="Q9" s="200"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
     </row>
     <row r="10" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="151">
@@ -16809,16 +19424,16 @@
       <c r="G10" s="145"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="200" t="s">
+      <c r="J10" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="K10" s="200"/>
-      <c r="L10" s="200"/>
-      <c r="M10" s="200"/>
-      <c r="N10" s="200"/>
-      <c r="O10" s="200"/>
-      <c r="P10" s="200"/>
-      <c r="Q10" s="200"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="124">
@@ -16833,16 +19448,16 @@
       <c r="G11" s="2"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
-      <c r="J11" s="200" t="s">
+      <c r="J11" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="K11" s="200"/>
-      <c r="L11" s="200"/>
-      <c r="M11" s="200"/>
-      <c r="N11" s="200"/>
-      <c r="O11" s="200"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
     </row>
     <row r="12" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="151">
@@ -16857,16 +19472,16 @@
       <c r="G12" s="145"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="200" t="s">
+      <c r="J12" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="K12" s="200"/>
-      <c r="L12" s="200"/>
-      <c r="M12" s="200"/>
-      <c r="N12" s="200"/>
-      <c r="O12" s="200"/>
-      <c r="P12" s="200"/>
-      <c r="Q12" s="200"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="124">
@@ -16881,16 +19496,16 @@
       <c r="G13" s="2"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
-      <c r="J13" s="200" t="s">
+      <c r="J13" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="K13" s="200"/>
-      <c r="L13" s="200"/>
-      <c r="M13" s="200"/>
-      <c r="N13" s="200"/>
-      <c r="O13" s="200"/>
-      <c r="P13" s="200"/>
-      <c r="Q13" s="200"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
     </row>
     <row r="14" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="151">
@@ -16905,18 +19520,16 @@
       <c r="G14" s="145"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="202" t="s">
+      <c r="J14" s="177" t="s">
         <v>386</v>
       </c>
-      <c r="K14" s="213"/>
-      <c r="L14" s="213"/>
-      <c r="M14" s="213"/>
-      <c r="N14" s="213"/>
-      <c r="O14" s="213"/>
-      <c r="P14" s="213"/>
-      <c r="Q14" s="213"/>
-      <c r="S14" s="214"/>
-      <c r="T14" s="214"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
@@ -16931,19 +19544,17 @@
       <c r="G15" s="2"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
-      <c r="J15" s="202" t="s">
+      <c r="J15" s="177" t="s">
         <v>380</v>
       </c>
-      <c r="K15" s="213"/>
-      <c r="L15" s="213"/>
-      <c r="M15" s="213"/>
-      <c r="N15" s="213"/>
-      <c r="O15" s="213"/>
-      <c r="P15" s="213"/>
-      <c r="Q15" s="215"/>
-      <c r="R15" s="214"/>
-      <c r="S15" s="226"/>
-      <c r="T15" s="214"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="185"/>
+      <c r="S15" s="195"/>
     </row>
     <row r="16" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="151">
@@ -16958,19 +19569,17 @@
       <c r="G16" s="145"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="202" t="s">
+      <c r="J16" s="177" t="s">
         <v>243</v>
       </c>
-      <c r="K16" s="213"/>
-      <c r="L16" s="213"/>
-      <c r="M16" s="213"/>
-      <c r="N16" s="213"/>
-      <c r="O16" s="213"/>
-      <c r="P16" s="213"/>
-      <c r="Q16" s="215"/>
-      <c r="R16" s="214"/>
-      <c r="S16" s="227"/>
-      <c r="T16" s="214"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="185"/>
+      <c r="S16" s="196"/>
     </row>
     <row r="17" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="124">
@@ -16985,19 +19594,17 @@
       <c r="G17" s="2"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="202" t="s">
+      <c r="J17" s="177" t="s">
         <v>359</v>
       </c>
-      <c r="K17" s="213"/>
-      <c r="L17" s="213"/>
-      <c r="M17" s="213"/>
-      <c r="N17" s="213"/>
-      <c r="O17" s="213"/>
-      <c r="P17" s="213"/>
-      <c r="Q17" s="215"/>
-      <c r="R17" s="214"/>
-      <c r="S17" s="227"/>
-      <c r="T17" s="214"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="185"/>
+      <c r="S17" s="196"/>
     </row>
     <row r="18" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="151">
@@ -17012,19 +19619,17 @@
       <c r="G18" s="145"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="202" t="s">
+      <c r="J18" s="177" t="s">
         <v>241</v>
       </c>
-      <c r="K18" s="213"/>
-      <c r="L18" s="213"/>
-      <c r="M18" s="213"/>
-      <c r="N18" s="213"/>
-      <c r="O18" s="213"/>
-      <c r="P18" s="213"/>
-      <c r="Q18" s="215"/>
-      <c r="R18" s="214"/>
-      <c r="S18" s="227"/>
-      <c r="T18" s="214"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="185"/>
+      <c r="S18" s="196"/>
     </row>
     <row r="19" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="124">
@@ -17039,19 +19644,17 @@
       <c r="G19" s="2"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="202" t="s">
+      <c r="J19" s="177" t="s">
         <v>239</v>
       </c>
-      <c r="K19" s="213"/>
-      <c r="L19" s="213"/>
-      <c r="M19" s="213"/>
-      <c r="N19" s="213"/>
-      <c r="O19" s="213"/>
-      <c r="P19" s="213"/>
-      <c r="Q19" s="215"/>
-      <c r="R19" s="214"/>
-      <c r="S19" s="227"/>
-      <c r="T19" s="214"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="185"/>
+      <c r="S19" s="196"/>
     </row>
     <row r="20" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="152">
@@ -17066,21 +19669,19 @@
       <c r="G20" s="145"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
-      <c r="J20" s="202" t="s">
+      <c r="J20" s="177" t="s">
         <v>384</v>
       </c>
-      <c r="K20" s="213"/>
-      <c r="L20" s="213"/>
-      <c r="M20" s="213"/>
-      <c r="N20" s="213"/>
-      <c r="O20" s="213"/>
-      <c r="P20" s="213"/>
-      <c r="Q20" s="215"/>
-      <c r="R20" s="214"/>
-      <c r="S20" s="227" t="s">
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="185"/>
+      <c r="S20" s="196" t="s">
         <v>382</v>
       </c>
-      <c r="T20" s="214"/>
     </row>
     <row r="21" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="93">
@@ -17095,21 +19696,19 @@
       <c r="G21" s="2"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
-      <c r="J21" s="202" t="s">
+      <c r="J21" s="177" t="s">
         <v>383</v>
       </c>
-      <c r="K21" s="213"/>
-      <c r="L21" s="213"/>
-      <c r="M21" s="213"/>
-      <c r="N21" s="213"/>
-      <c r="O21" s="213"/>
-      <c r="P21" s="213"/>
-      <c r="Q21" s="215"/>
-      <c r="R21" s="214"/>
-      <c r="S21" s="227" t="s">
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="185"/>
+      <c r="S21" s="196" t="s">
         <v>382</v>
       </c>
-      <c r="T21" s="214"/>
     </row>
     <row r="22" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="152">
@@ -17124,90 +19723,86 @@
       <c r="G22" s="9"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="216" t="s">
+      <c r="J22" s="186" t="s">
         <v>240</v>
       </c>
-      <c r="K22" s="197"/>
-      <c r="L22" s="197"/>
-      <c r="M22" s="197"/>
-      <c r="N22" s="197"/>
-      <c r="O22" s="197"/>
-      <c r="P22" s="197"/>
-      <c r="Q22" s="215"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="228" t="s">
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="185"/>
+      <c r="S22" s="197" t="s">
         <v>382</v>
       </c>
-      <c r="T22" s="214"/>
     </row>
     <row r="23" spans="1:21" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="218"/>
-      <c r="B23" s="219"/>
-      <c r="C23" s="219"/>
-      <c r="D23" s="219"/>
-      <c r="E23" s="219"/>
-      <c r="F23" s="219"/>
-      <c r="G23" s="219"/>
-      <c r="H23" s="219"/>
-      <c r="I23" s="219"/>
-      <c r="J23" s="219"/>
-      <c r="K23" s="219"/>
-      <c r="L23" s="219"/>
-      <c r="M23" s="219"/>
-      <c r="N23" s="219"/>
-      <c r="O23" s="219"/>
-      <c r="P23" s="219"/>
-      <c r="Q23" s="229" t="s">
+      <c r="A23" s="187"/>
+      <c r="B23" s="188"/>
+      <c r="C23" s="188"/>
+      <c r="D23" s="188"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="188"/>
+      <c r="I23" s="188"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="188"/>
+      <c r="L23" s="188"/>
+      <c r="M23" s="188"/>
+      <c r="N23" s="188"/>
+      <c r="O23" s="188"/>
+      <c r="P23" s="188"/>
+      <c r="Q23" s="198" t="s">
         <v>385</v>
       </c>
-      <c r="S23" s="214"/>
-      <c r="T23" s="214"/>
     </row>
     <row r="24" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="185" t="s">
+      <c r="A24" s="219" t="s">
         <v>206</v>
       </c>
-      <c r="B24" s="186"/>
-      <c r="C24" s="217" t="s">
+      <c r="B24" s="220"/>
+      <c r="C24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="217" t="s">
+      <c r="D24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="217" t="s">
+      <c r="E24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="217" t="s">
+      <c r="F24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="217" t="s">
+      <c r="G24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="217" t="s">
+      <c r="H24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="217" t="s">
+      <c r="I24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="217" t="s">
+      <c r="J24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="217" t="s">
+      <c r="K24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="217" t="s">
+      <c r="L24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="217" t="s">
+      <c r="M24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="N24" s="217" t="s">
+      <c r="N24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="217" t="s">
+      <c r="O24" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="217" t="s">
+      <c r="P24" s="149" t="s">
         <v>8</v>
       </c>
       <c r="Q24" s="149" t="s">
@@ -17282,10 +19877,10 @@
       <c r="U25" s="1"/>
     </row>
     <row r="26" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="187">
+      <c r="A26" s="221">
         <v>19</v>
       </c>
-      <c r="B26" s="188"/>
+      <c r="B26" s="222"/>
       <c r="C26" s="147">
         <f>$A26-C$25</f>
         <v>22</v>
@@ -17348,10 +19943,10 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="189">
+      <c r="A27" s="223">
         <v>18</v>
       </c>
-      <c r="B27" s="190"/>
+      <c r="B27" s="224"/>
       <c r="C27" s="148">
         <f t="shared" ref="C27:Q34" si="3">$A27-C$25</f>
         <v>21</v>
@@ -17414,10 +20009,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="188">
+      <c r="A28" s="222">
         <v>17</v>
       </c>
-      <c r="B28" s="188"/>
+      <c r="B28" s="222"/>
       <c r="C28" s="147">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -17480,10 +20075,10 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="190">
+      <c r="A29" s="224">
         <v>16</v>
       </c>
-      <c r="B29" s="190"/>
+      <c r="B29" s="224"/>
       <c r="C29" s="148">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -17546,10 +20141,10 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="188">
+      <c r="A30" s="222">
         <v>15</v>
       </c>
-      <c r="B30" s="188"/>
+      <c r="B30" s="222"/>
       <c r="C30" s="147">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -17612,10 +20207,10 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="190">
+      <c r="A31" s="224">
         <v>14</v>
       </c>
-      <c r="B31" s="190"/>
+      <c r="B31" s="224"/>
       <c r="C31" s="148">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -17678,10 +20273,10 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="188">
+      <c r="A32" s="222">
         <v>13</v>
       </c>
-      <c r="B32" s="188"/>
+      <c r="B32" s="222"/>
       <c r="C32" s="147">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -17744,10 +20339,10 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="190">
+      <c r="A33" s="224">
         <v>12</v>
       </c>
-      <c r="B33" s="190"/>
+      <c r="B33" s="224"/>
       <c r="C33" s="148">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -17810,10 +20405,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="188">
+      <c r="A34" s="222">
         <v>11</v>
       </c>
-      <c r="B34" s="188"/>
+      <c r="B34" s="222"/>
       <c r="C34" s="147">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -17876,44 +20471,44 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="220"/>
-      <c r="B35" s="221"/>
-      <c r="C35" s="220"/>
-      <c r="D35" s="220"/>
-      <c r="E35" s="220"/>
-      <c r="F35" s="220"/>
-      <c r="G35" s="220"/>
-      <c r="H35" s="220"/>
-      <c r="I35" s="220"/>
-      <c r="J35" s="220"/>
-      <c r="K35" s="220"/>
-      <c r="L35" s="220"/>
-      <c r="M35" s="220"/>
-      <c r="N35" s="220"/>
-      <c r="O35" s="220"/>
-      <c r="P35" s="220"/>
-      <c r="Q35" s="222" t="s">
+      <c r="A35" s="189"/>
+      <c r="B35" s="190"/>
+      <c r="C35" s="189"/>
+      <c r="D35" s="189"/>
+      <c r="E35" s="189"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="189"/>
+      <c r="H35" s="189"/>
+      <c r="I35" s="189"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="189"/>
+      <c r="L35" s="189"/>
+      <c r="M35" s="189"/>
+      <c r="N35" s="189"/>
+      <c r="O35" s="189"/>
+      <c r="P35" s="189"/>
+      <c r="Q35" s="191" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="223"/>
-      <c r="B36" s="224"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="223"/>
-      <c r="K36" s="223"/>
-      <c r="L36" s="223"/>
-      <c r="M36" s="223"/>
-      <c r="N36" s="223"/>
-      <c r="O36" s="223"/>
-      <c r="P36" s="223"/>
-      <c r="Q36" s="223"/>
+      <c r="A36" s="192"/>
+      <c r="B36" s="193"/>
+      <c r="C36" s="192"/>
+      <c r="D36" s="192"/>
+      <c r="E36" s="192"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="192"/>
+      <c r="H36" s="192"/>
+      <c r="I36" s="192"/>
+      <c r="J36" s="192"/>
+      <c r="K36" s="192"/>
+      <c r="L36" s="192"/>
+      <c r="M36" s="192"/>
+      <c r="N36" s="192"/>
+      <c r="O36" s="192"/>
+      <c r="P36" s="192"/>
+      <c r="Q36" s="192"/>
     </row>
     <row r="37" spans="1:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="96" t="s">
@@ -18268,7 +20863,7 @@
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
       <c r="J48" s="3"/>
-      <c r="Q48" s="230" t="s">
+      <c r="Q48" s="199" t="s">
         <v>388</v>
       </c>
     </row>
@@ -18356,19 +20951,19 @@
       <c r="E1" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="191" t="s">
+      <c r="F1" s="225" t="s">
         <v>356</v>
       </c>
-      <c r="G1" s="191"/>
-      <c r="H1" s="191"/>
-      <c r="I1" s="191"/>
-      <c r="J1" s="191"/>
-      <c r="K1" s="191"/>
-      <c r="L1" s="191"/>
-      <c r="M1" s="191"/>
-      <c r="N1" s="191"/>
-      <c r="O1" s="191"/>
-      <c r="P1" s="191"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
     </row>
     <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="166" t="s">
@@ -18777,19 +21372,19 @@
       <c r="E25" s="164" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="194" t="s">
+      <c r="F25" s="173" t="s">
         <v>357</v>
       </c>
-      <c r="G25" s="195"/>
-      <c r="H25" s="195"/>
-      <c r="I25" s="195"/>
-      <c r="J25" s="195"/>
-      <c r="K25" s="195"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="195"/>
-      <c r="N25" s="195"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="196" t="s">
+      <c r="G25" s="174"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="174"/>
+      <c r="M25" s="174"/>
+      <c r="N25" s="174"/>
+      <c r="O25" s="174"/>
+      <c r="P25" s="175" t="s">
         <v>358</v>
       </c>
     </row>
@@ -18806,7 +21401,7 @@
       <c r="D26" s="170" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="193" t="s">
+      <c r="E26" s="172" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18964,11 +21559,11 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="192"/>
-      <c r="B36" s="192"/>
-      <c r="C36" s="192"/>
-      <c r="D36" s="192"/>
-      <c r="E36" s="192"/>
+      <c r="A36" s="171"/>
+      <c r="B36" s="171"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
+      <c r="E36" s="171"/>
     </row>
     <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="166" t="s">
@@ -18988,19 +21583,19 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="192" t="s">
+      <c r="A38" s="171" t="s">
         <v>310</v>
       </c>
-      <c r="B38" s="192">
+      <c r="B38" s="171">
         <v>2</v>
       </c>
-      <c r="C38" s="192" t="s">
+      <c r="C38" s="171" t="s">
         <v>292</v>
       </c>
-      <c r="D38" s="192">
+      <c r="D38" s="171">
         <v>1</v>
       </c>
-      <c r="E38" s="192" t="s">
+      <c r="E38" s="171" t="s">
         <v>316</v>
       </c>
     </row>
@@ -19022,19 +21617,19 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="192" t="s">
+      <c r="A40" s="171" t="s">
         <v>312</v>
       </c>
-      <c r="B40" s="192">
+      <c r="B40" s="171">
         <v>3</v>
       </c>
-      <c r="C40" s="192" t="s">
+      <c r="C40" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="D40" s="192">
+      <c r="D40" s="171">
         <v>1</v>
       </c>
-      <c r="E40" s="192" t="s">
+      <c r="E40" s="171" t="s">
         <v>318</v>
       </c>
     </row>

--- a/Strumenti/Schede_DnD_BX91.xlsx
+++ b/Strumenti/Schede_DnD_BX91.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Public\_Clienti\Maruga\Giochi\Vampiri\Vault\Vampiri\Strumenti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D30BE5-90D0-4178-9C86-FB20DECDDE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9C7BB4-2B55-471B-A393-6EB359E29C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23412" yWindow="0" windowWidth="24336" windowHeight="16656" firstSheet="1" activeTab="9" xr2:uid="{FC328CB3-F1C2-4520-956D-C4D288DB9EEB}"/>
+    <workbookView xWindow="22224" yWindow="0" windowWidth="24336" windowHeight="16656" firstSheet="1" activeTab="9" xr2:uid="{FC328CB3-F1C2-4520-956D-C4D288DB9EEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Halfling A" sheetId="8" r:id="rId1"/>
@@ -22,8 +22,7 @@
     <sheet name="Cleric A" sheetId="1" r:id="rId7"/>
     <sheet name="Retro" sheetId="2" r:id="rId8"/>
     <sheet name="Arcade" sheetId="9" r:id="rId9"/>
-    <sheet name="Citta" sheetId="11" r:id="rId10"/>
-    <sheet name="Foglio3" sheetId="12" r:id="rId11"/>
+    <sheet name="Empori" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="684">
   <si>
     <t>Giocatore</t>
   </si>
@@ -1216,9 +1215,6 @@
     <t>by maru</t>
   </si>
   <si>
-    <t>--- VILLAGGIO (e superiori) ---</t>
-  </si>
-  <si>
     <t>Razione (1 giorno)</t>
   </si>
   <si>
@@ -1267,9 +1263,6 @@
     <t>Acciarino e pietra focaia</t>
   </si>
   <si>
-    <t>Accendere fuoco: 1 round.</t>
-  </si>
-  <si>
     <t>Piantare chiodi/paletti. Come arma improvvisata: 1d4.</t>
   </si>
   <si>
@@ -1360,9 +1353,6 @@
     <t>Conosce la zona. Morale 7. Non combatte.</t>
   </si>
   <si>
-    <t>--- PAESE (e superiori) ---</t>
-  </si>
-  <si>
     <t>Razione secca (1 settimana)</t>
   </si>
   <si>
@@ -1393,12 +1383,6 @@
     <t>Luce 30', 4 ore per fiasca olio. Vento non la spegne.</t>
   </si>
   <si>
-    <t>Lanciato 10'/20'/30': TxC vs CA 9. 1d8 fuoco, brucia 2 round (1d8/round).</t>
-  </si>
-  <si>
-    <t>Blocca porta: nemico deve sfondare. Rimuovere: 1 turno (1 round con martello).</t>
-  </si>
-  <si>
     <t>Borse da sella</t>
   </si>
   <si>
@@ -1471,9 +1455,6 @@
     <t>Trasporta 6 persone. Movimento 30'.</t>
   </si>
   <si>
-    <t>--- PICCOLA CITTÀ (e superiori) ---</t>
-  </si>
-  <si>
     <t>Guardare angoli. Riflette sguardo pietrificante: mostro TS Pietrificazione o subisce effetto.</t>
   </si>
   <si>
@@ -1519,9 +1500,6 @@
     <t>Balestra leggera</t>
   </si>
   <si>
-    <t>1d6 danni. Gittata 60'/120'/180'. Due mani. Ricarica 1 round.</t>
-  </si>
-  <si>
     <t>Armatura borchiata</t>
   </si>
   <si>
@@ -1588,12 +1566,6 @@
     <t>Mago/Elfo/Chierico. Malvagi -1 TxC, +1 TS. Evocati non toccano. Durata 12 turni.</t>
   </si>
   <si>
-    <t>Solo Chierico. Cura 1d6+1 HP. Tocco. Alternativa: 1d6+1 danni a non-morti (TxC).</t>
-  </si>
-  <si>
-    <t>--- MEDIA/GRANDE CITTÀ ---</t>
-  </si>
-  <si>
     <t>Spada a due mani</t>
   </si>
   <si>
@@ -1606,9 +1578,6 @@
     <t>Balestra pesante</t>
   </si>
   <si>
-    <t>1d8 danni. Gittata 80'/160'/240'. Due mani. Ricarica 2 round.</t>
-  </si>
-  <si>
     <t>Armatura a scaglie</t>
   </si>
   <si>
@@ -1708,9 +1677,6 @@
     <t>Pergamena: Rimuovi Paralisi</t>
   </si>
   <si>
-    <t>Solo Chierico. Rimuove paralisi da 1d4 creature. Consigliata.</t>
-  </si>
-  <si>
     <t>Pergamena: Dissolvi Magie</t>
   </si>
   <si>
@@ -1726,12 +1692,6 @@
     <t>Pergamena: Blocca Persone</t>
   </si>
   <si>
-    <t>Mago/Elfo/Chierico. Paralizza 1d4 umanoidi. TS nega. Durata 1 turno +1/livello.</t>
-  </si>
-  <si>
-    <t>--- RARO (richiede ricerca o contatti) ---</t>
-  </si>
-  <si>
     <t>Spada corta +1</t>
   </si>
   <si>
@@ -1832,6 +1792,312 @@
   </si>
   <si>
     <t>Contiene 500 mo di peso, pesa sempre 5 mo.</t>
+  </si>
+  <si>
+    <t>--- EMPORIO ---</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>--- ARMERIA ---</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>--- STALLA ---</t>
+  </si>
+  <si>
+    <t>--- TEMPIO ---</t>
+  </si>
+  <si>
+    <t>Servizio: Cura Ferite Leggere</t>
+  </si>
+  <si>
+    <t>Chierico cura 1d6+1 HP.</t>
+  </si>
+  <si>
+    <t>Servizio: Cura Malattie</t>
+  </si>
+  <si>
+    <t>Chierico rimuove una malattia.</t>
+  </si>
+  <si>
+    <t>Servizio: Rimuovi Maledizione</t>
+  </si>
+  <si>
+    <t>Chierico rimuove una maledizione.</t>
+  </si>
+  <si>
+    <t>Servizio: Resuscitare Morti</t>
+  </si>
+  <si>
+    <t>--- BOTTEGA DEL MAGO ---</t>
+  </si>
+  <si>
+    <t>--- RARO (ricerca/contatti) ---</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>--- SERVIZI ---</t>
+  </si>
+  <si>
+    <t>Lanciato 10'/20'/30': TxC vs CA 9. 1d8 fuoco, brucia 2 R (1d8/R).</t>
+  </si>
+  <si>
+    <t>Accendere fuoco: 1 R.</t>
+  </si>
+  <si>
+    <t>Blocca porta: nemico deve sfondare. Rimuovere: 1 turno (1 R con martello).</t>
+  </si>
+  <si>
+    <t>1d6 danni. Gittata 60'/120'/180'. Due mani. Ricarica 1 R.</t>
+  </si>
+  <si>
+    <t>1d8 danni. Gittata 80'/160'/240'. Due mani. Ricarica 2 R.</t>
+  </si>
+  <si>
+    <t>Pozioni Cura — "Bevi prima di morire!"   /   Pergamena Fulmine — "60 piedi di 'non mi hai sentito la prima volta'."</t>
+  </si>
+  <si>
+    <t>Paletti argento (3)</t>
+  </si>
+  <si>
+    <t>Come legno. Funziona anche su licantropi paralizzati.</t>
+  </si>
+  <si>
+    <t>Incenso sacro (6 bastoncini)</t>
+  </si>
+  <si>
+    <t>Brucia 1 ora. Spiriti minori evitano l'area 10'.</t>
+  </si>
+  <si>
+    <t>Candele benedette (6)</t>
+  </si>
+  <si>
+    <t>Luce 5', 2 ore. Non-morti -1 TxC entro la luce.</t>
+  </si>
+  <si>
+    <t>Olio sacro (fiala)</t>
+  </si>
+  <si>
+    <t>Unge arma: +1 danno vs non-morti per 1 combattimento.</t>
+  </si>
+  <si>
+    <t>Sale consacrato (sacchetto)</t>
+  </si>
+  <si>
+    <t>Linea di sale: non-morti minori (1 DV) non attraversano.</t>
+  </si>
+  <si>
+    <t>Testo sacro</t>
+  </si>
+  <si>
+    <t>Libro delle preghiere. Necessario per alcuni rituali.</t>
+  </si>
+  <si>
+    <t>Cero funerario (3)</t>
+  </si>
+  <si>
+    <t>Impedisce a un cadavere di risorgere come non-morto per 24 ore.</t>
+  </si>
+  <si>
+    <t>Pergamena: Purifica Cibo e Acqua</t>
+  </si>
+  <si>
+    <t>Pergamena: Silenzio 15'</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Nessun suono in area 15'. Blocca incantesimi verbali. Durata 12 turni.</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Paralizza 1d4 umanoidi. TS nega. Durata 1 turno +1/livello.</t>
+  </si>
+  <si>
+    <t>Pergamena: Parlare con Animali</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Comunica con animali normali. Durata 6 turni.</t>
+  </si>
+  <si>
+    <t>Pergamena: Trovare Trappole</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Rileva trappole entro 30'. Durata 2 turni.</t>
+  </si>
+  <si>
+    <t>Pergamena: Cura Malattie</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Rimuove qualsiasi malattia. Tocco.</t>
+  </si>
+  <si>
+    <t>Pergamena: Cura Ferite Gravi</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Cura 2d6+2 HP. Tocco.</t>
+  </si>
+  <si>
+    <t>Pergamena: Neutralizza Veleno</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Rimuove qualsiasi veleno. Tocco.</t>
+  </si>
+  <si>
+    <t>Servizio: Benedizione viaggio</t>
+  </si>
+  <si>
+    <t>+1 primo TS del giorno. Dura fino al tramonto.</t>
+  </si>
+  <si>
+    <t>Servizio: Neutralizza Veleno</t>
+  </si>
+  <si>
+    <t>Chierico rimuove veleno dal corpo.</t>
+  </si>
+  <si>
+    <t>Chierico riporta in vita (max 4 giorni dalla morte). TS Veleno o fallisce.</t>
+  </si>
+  <si>
+    <t>Servizio: Sepoltura consacrata</t>
+  </si>
+  <si>
+    <t>Rito funebre. Impedisce resurrezione come non-morto.</t>
+  </si>
+  <si>
+    <t>Servizio: Consacrazione acqua</t>
+  </si>
+  <si>
+    <t>Trasforma 1 fiala d'acqua in acqua santa.</t>
+  </si>
+  <si>
+    <t>Donazione (alloggio tempio)</t>
+  </si>
+  <si>
+    <t>Letto in dormitorio comune. Pasto frugale incluso.</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Cura 1d6+1 HP. Tocco.</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Purifica cibo/acqua per 12 persone.</t>
+  </si>
+  <si>
+    <t>Solo Chierico. Rimuove paralisi da 1d4 creature.</t>
+  </si>
+  <si>
+    <t>Turibolo (incensiere)</t>
+  </si>
+  <si>
+    <t>Diffonde incenso in area 20'. Necessario per rituali di purificazione.</t>
+  </si>
+  <si>
+    <t>Fiala vuota benedetta</t>
+  </si>
+  <si>
+    <t>Può contenere acqua santa senza perdere proprietà.</t>
+  </si>
+  <si>
+    <t>Unguento curativo (3 usi)</t>
+  </si>
+  <si>
+    <t>Cura 1 HP per uso. Non magico. Applicare richiede 1 turno.</t>
+  </si>
+  <si>
+    <t>Pozione Lettura Linguaggi</t>
+  </si>
+  <si>
+    <t>Durata 2 turni. Legge qualsiasi lingua scritta (non codici magici).</t>
+  </si>
+  <si>
+    <t>Pozione ESP</t>
+  </si>
+  <si>
+    <t>Durata 6 turni. Legge pensieri entro 60'. Bloccata da 60cm di pietra.</t>
+  </si>
+  <si>
+    <t>Pozione Respirare Sott'acqua</t>
+  </si>
+  <si>
+    <t>Durata 4 ore. Respira normalmente sott'acqua.</t>
+  </si>
+  <si>
+    <t>Pozione Crescita</t>
+  </si>
+  <si>
+    <t>Durata 2 turni. Raddoppia dimensioni. FOR +4, danni x2.</t>
+  </si>
+  <si>
+    <t>Pozione Diminuzione</t>
+  </si>
+  <si>
+    <t>Durata 2 turni. Riduce a 15cm. CA +4 vs creature grandi.</t>
+  </si>
+  <si>
+    <t>Pozione Scurovisione</t>
+  </si>
+  <si>
+    <t>Durata 6 turni. Vede al buio 60' (bianco e nero).</t>
+  </si>
+  <si>
+    <t>Inchiostro magico (fiala)</t>
+  </si>
+  <si>
+    <t>Necessario per copiare incantesimi. 1 fiala = 1 incantesimo.</t>
+  </si>
+  <si>
+    <t>Pergamena: Lettura Linguaggi</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Legge qualsiasi lingua scritta. Durata 2 turni.</t>
+  </si>
+  <si>
+    <t>Pergamena: Scurovisione</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Vede al buio 60'. Durata 6 turni.</t>
+  </si>
+  <si>
+    <t>Pergamena: Volare</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Movimento 120'. Durata 1d6 turni +1/livello.</t>
+  </si>
+  <si>
+    <t>Pergamena: Velocità</t>
+  </si>
+  <si>
+    <t>Solo Mago/Elfo. Movimento x2, 2 attacchi/round. Durata 3 turni.</t>
+  </si>
+  <si>
+    <t>Servizio: Identificazione oggetto</t>
+  </si>
+  <si>
+    <t>Mago identifica proprietà di 1 oggetto magico.</t>
+  </si>
+  <si>
+    <t>Servizio: Lettura pergamena</t>
+  </si>
+  <si>
+    <t>Mago legge una pergamena non magica in lingua sconosciuta.</t>
+  </si>
+  <si>
+    <t>V = Villaggio</t>
+  </si>
+  <si>
+    <t>P = Paese</t>
+  </si>
+  <si>
+    <t>C = Piccola Città</t>
+  </si>
+  <si>
+    <t>G = Media/Grande Città</t>
+  </si>
+  <si>
+    <t>R = Raro (ricerca/contatti)</t>
   </si>
 </sst>
 </file>
@@ -1842,7 +2108,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2169,6 +2435,17 @@
     <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -2549,7 +2826,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3207,6 +3484,75 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -11233,2005 +11579,3419 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5B8450-D323-4BD0-AC14-7E0806B219F9}">
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P244"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" style="166" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" style="165" customWidth="1"/>
-    <col min="3" max="3" width="9" style="165" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" style="165" customWidth="1"/>
-    <col min="5" max="5" width="52.21875" style="164" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="164"/>
+    <col min="1" max="1" width="27.5546875" style="234" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" style="240" customWidth="1"/>
+    <col min="3" max="3" width="9" style="235" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="235" customWidth="1"/>
+    <col min="5" max="5" width="52.21875" style="236" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="226" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="226"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="168"/>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="225" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="232" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="233" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="233" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" s="233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="232" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="229"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="229"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="238" t="s">
+        <v>582</v>
+      </c>
+      <c r="B3" s="238"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="234" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="235">
+        <v>1</v>
+      </c>
+      <c r="E4" s="236" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="241" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="242" t="s">
+        <v>436</v>
+      </c>
+      <c r="D5" s="242">
+        <v>7</v>
+      </c>
+      <c r="E5" s="243" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="234" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="235">
+        <v>1</v>
+      </c>
+      <c r="E6" s="236" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="241" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="242">
+        <v>1</v>
+      </c>
+      <c r="E7" s="243" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="234" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="235">
+        <v>1</v>
+      </c>
+      <c r="E8" s="236" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="241" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="242">
+        <v>2</v>
+      </c>
+      <c r="E9" s="243" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="234" t="s">
+        <v>440</v>
+      </c>
+      <c r="B10" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" s="235">
+        <v>1</v>
+      </c>
+      <c r="E10" s="236" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="241" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="242">
+        <v>2</v>
+      </c>
+      <c r="E11" s="243" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="234" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="235" t="s">
+        <v>272</v>
+      </c>
+      <c r="D12" s="235">
+        <v>1</v>
+      </c>
+      <c r="E12" s="236" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="241" t="s">
+        <v>396</v>
+      </c>
+      <c r="B13" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="242" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="242">
+        <v>3</v>
+      </c>
+      <c r="E13" s="243" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="234" t="s">
+        <v>399</v>
+      </c>
+      <c r="B14" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C14" s="235" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" s="235">
+        <v>2</v>
+      </c>
+      <c r="E14" s="236" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="241" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C15" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D15" s="242">
+        <v>1</v>
+      </c>
+      <c r="E15" s="243" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="234" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C16" s="235" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" s="235">
+        <v>1</v>
+      </c>
+      <c r="E16" s="236" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="241" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C17" s="242" t="s">
+        <v>272</v>
+      </c>
+      <c r="D17" s="242">
+        <v>1</v>
+      </c>
+      <c r="E17" s="243" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="234" t="s">
+        <v>402</v>
+      </c>
+      <c r="B18" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C18" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E18" s="236" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="241" t="s">
+        <v>404</v>
+      </c>
+      <c r="B19" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C19" s="242" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E19" s="243" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="234" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C20" s="235" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="235">
+        <v>1</v>
+      </c>
+      <c r="E20" s="236" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="241" t="s">
+        <v>273</v>
+      </c>
+      <c r="B21" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C21" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="242">
+        <v>1</v>
+      </c>
+      <c r="E21" s="243" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="B22" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C22" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="236" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="241" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C23" s="242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" s="243" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="234" t="s">
+        <v>473</v>
+      </c>
+      <c r="B24" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C24" s="235" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E24" s="236" t="s">
+        <v>474</v>
+      </c>
+      <c r="F24" s="237"/>
+      <c r="G24" s="237"/>
+      <c r="H24" s="237"/>
+      <c r="I24" s="237"/>
+      <c r="J24" s="237"/>
+      <c r="K24" s="237"/>
+      <c r="L24" s="237"/>
+      <c r="M24" s="237"/>
+      <c r="N24" s="237"/>
+      <c r="O24" s="237"/>
+      <c r="P24" s="237"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="241" t="s">
+        <v>445</v>
+      </c>
+      <c r="B25" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C25" s="242" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" s="242">
+        <v>1</v>
+      </c>
+      <c r="E25" s="243" t="s">
+        <v>446</v>
+      </c>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="227"/>
+      <c r="I25" s="227"/>
+      <c r="J25" s="227"/>
+      <c r="K25" s="227"/>
+      <c r="L25" s="227"/>
+      <c r="M25" s="227"/>
+      <c r="N25" s="227"/>
+      <c r="O25" s="227"/>
+      <c r="P25" s="228"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F26" s="227"/>
+      <c r="G26" s="227"/>
+      <c r="H26" s="227"/>
+      <c r="I26" s="227"/>
+      <c r="J26" s="227"/>
+      <c r="K26" s="227"/>
+      <c r="L26" s="227"/>
+      <c r="M26" s="227"/>
+      <c r="N26" s="227"/>
+      <c r="O26" s="227"/>
+      <c r="P26" s="228"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="238" t="s">
+        <v>586</v>
+      </c>
+      <c r="B27" s="238"/>
+      <c r="C27" s="238"/>
+      <c r="D27" s="238"/>
+      <c r="E27" s="238"/>
+      <c r="F27" s="227"/>
+      <c r="G27" s="227"/>
+      <c r="H27" s="227"/>
+      <c r="I27" s="227"/>
+      <c r="J27" s="227"/>
+      <c r="K27" s="227"/>
+      <c r="L27" s="227"/>
+      <c r="M27" s="227"/>
+      <c r="N27" s="227"/>
+      <c r="O27" s="227"/>
+      <c r="P27" s="228"/>
+    </row>
+    <row r="28" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="234" t="s">
+        <v>424</v>
+      </c>
+      <c r="B28" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C28" s="235" t="s">
+        <v>425</v>
+      </c>
+      <c r="D28" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E28" s="236" t="s">
+        <v>426</v>
+      </c>
+      <c r="F28" s="227"/>
+      <c r="G28" s="227"/>
+      <c r="H28" s="227"/>
+      <c r="I28" s="227"/>
+      <c r="J28" s="227"/>
+      <c r="K28" s="227"/>
+      <c r="L28" s="227"/>
+      <c r="M28" s="227"/>
+      <c r="N28" s="227"/>
+      <c r="O28" s="227"/>
+      <c r="P28" s="228"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="241" t="s">
+        <v>427</v>
+      </c>
+      <c r="B29" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C29" s="242" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E29" s="243" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="227"/>
+      <c r="G29" s="227"/>
+      <c r="H29" s="227"/>
+      <c r="I29" s="227"/>
+      <c r="J29" s="227"/>
+      <c r="K29" s="227"/>
+      <c r="L29" s="227"/>
+      <c r="M29" s="227"/>
+      <c r="N29" s="227"/>
+      <c r="O29" s="227"/>
+      <c r="P29" s="228"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="234" t="s">
+        <v>429</v>
+      </c>
+      <c r="B30" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C30" s="235" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E30" s="236" t="s">
+        <v>430</v>
+      </c>
+      <c r="F30" s="227"/>
+      <c r="G30" s="227"/>
+      <c r="H30" s="227"/>
+      <c r="I30" s="227"/>
+      <c r="J30" s="227"/>
+      <c r="K30" s="227"/>
+      <c r="L30" s="227"/>
+      <c r="M30" s="227"/>
+      <c r="N30" s="227"/>
+      <c r="O30" s="227"/>
+      <c r="P30" s="228"/>
+    </row>
+    <row r="31" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="241" t="s">
+        <v>458</v>
+      </c>
+      <c r="B31" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C31" s="242" t="s">
+        <v>459</v>
+      </c>
+      <c r="D31" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E31" s="243" t="s">
+        <v>460</v>
+      </c>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="227"/>
+      <c r="I31" s="227"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="227"/>
+      <c r="L31" s="227"/>
+      <c r="M31" s="227"/>
+      <c r="N31" s="227"/>
+      <c r="O31" s="227"/>
+      <c r="P31" s="228"/>
+    </row>
+    <row r="32" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="234" t="s">
+        <v>516</v>
+      </c>
+      <c r="B32" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C32" s="235" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" s="236" t="s">
+        <v>517</v>
+      </c>
+      <c r="F32" s="227"/>
+      <c r="G32" s="227"/>
+      <c r="H32" s="227"/>
+      <c r="I32" s="227"/>
+      <c r="J32" s="227"/>
+      <c r="K32" s="227"/>
+      <c r="L32" s="227"/>
+      <c r="M32" s="227"/>
+      <c r="N32" s="227"/>
+      <c r="O32" s="227"/>
+      <c r="P32" s="228"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="241" t="s">
+        <v>461</v>
+      </c>
+      <c r="B33" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C33" s="242" t="s">
+        <v>313</v>
+      </c>
+      <c r="D33" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E33" s="243" t="s">
+        <v>462</v>
+      </c>
+      <c r="F33" s="227"/>
+      <c r="G33" s="227"/>
+      <c r="H33" s="227"/>
+      <c r="I33" s="227"/>
+      <c r="J33" s="227"/>
+      <c r="K33" s="227"/>
+      <c r="L33" s="227"/>
+      <c r="M33" s="227"/>
+      <c r="N33" s="227"/>
+      <c r="O33" s="227"/>
+      <c r="P33" s="228"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="234" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C34" s="235" t="s">
+        <v>313</v>
+      </c>
+      <c r="D34" s="235">
+        <v>2</v>
+      </c>
+      <c r="E34" s="236" t="s">
+        <v>464</v>
+      </c>
+      <c r="F34" s="227"/>
+      <c r="G34" s="227"/>
+      <c r="H34" s="227"/>
+      <c r="I34" s="227"/>
+      <c r="J34" s="227"/>
+      <c r="K34" s="227"/>
+      <c r="L34" s="227"/>
+      <c r="M34" s="227"/>
+      <c r="N34" s="227"/>
+      <c r="O34" s="227"/>
+      <c r="P34" s="228"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="241" t="s">
+        <v>465</v>
+      </c>
+      <c r="B35" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C35" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D35" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E35" s="243" t="s">
+        <v>466</v>
+      </c>
+      <c r="F35" s="227"/>
+      <c r="G35" s="227"/>
+      <c r="H35" s="227"/>
+      <c r="I35" s="227"/>
+      <c r="J35" s="227"/>
+      <c r="K35" s="227"/>
+      <c r="L35" s="227"/>
+      <c r="M35" s="227"/>
+      <c r="N35" s="227"/>
+      <c r="O35" s="227"/>
+      <c r="P35" s="228"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="234" t="s">
+        <v>467</v>
+      </c>
+      <c r="B36" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C36" s="235" t="s">
+        <v>292</v>
+      </c>
+      <c r="D36" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E36" s="236" t="s">
+        <v>468</v>
+      </c>
+      <c r="F36" s="227"/>
+      <c r="G36" s="227"/>
+      <c r="H36" s="227"/>
+      <c r="I36" s="227"/>
+      <c r="J36" s="227"/>
+      <c r="K36" s="227"/>
+      <c r="L36" s="227"/>
+      <c r="M36" s="227"/>
+      <c r="N36" s="227"/>
+      <c r="O36" s="227"/>
+      <c r="P36" s="228"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F37" s="227"/>
+      <c r="G37" s="227"/>
+      <c r="H37" s="227"/>
+      <c r="I37" s="227"/>
+      <c r="J37" s="227"/>
+      <c r="K37" s="227"/>
+      <c r="L37" s="227"/>
+      <c r="M37" s="227"/>
+      <c r="N37" s="227"/>
+      <c r="O37" s="227"/>
+      <c r="P37" s="228"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="238" t="s">
+        <v>598</v>
+      </c>
+      <c r="B38" s="238"/>
+      <c r="C38" s="238"/>
+      <c r="D38" s="238"/>
+      <c r="E38" s="238"/>
+      <c r="F38" s="227"/>
+      <c r="G38" s="227"/>
+      <c r="H38" s="227"/>
+      <c r="I38" s="227"/>
+      <c r="J38" s="227"/>
+      <c r="K38" s="227"/>
+      <c r="L38" s="227"/>
+      <c r="M38" s="227"/>
+      <c r="N38" s="227"/>
+      <c r="O38" s="227"/>
+      <c r="P38" s="228"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="234" t="s">
+        <v>431</v>
+      </c>
+      <c r="B39" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C39" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E39" s="236" t="s">
+        <v>432</v>
+      </c>
+      <c r="F39" s="227"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="227"/>
+      <c r="I39" s="227"/>
+      <c r="J39" s="227"/>
+      <c r="K39" s="227"/>
+      <c r="L39" s="227"/>
+      <c r="M39" s="227"/>
+      <c r="N39" s="227"/>
+      <c r="O39" s="227"/>
+      <c r="P39" s="228"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="241" t="s">
+        <v>433</v>
+      </c>
+      <c r="B40" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C40" s="242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D40" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E40" s="243" t="s">
+        <v>434</v>
+      </c>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
+      <c r="O40" s="227"/>
+      <c r="P40" s="228"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="234" t="s">
+        <v>490</v>
+      </c>
+      <c r="B41" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C41" s="235" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E41" s="236" t="s">
+        <v>491</v>
+      </c>
+      <c r="F41" s="227"/>
+      <c r="G41" s="227"/>
+      <c r="H41" s="227"/>
+      <c r="I41" s="227"/>
+      <c r="J41" s="227"/>
+      <c r="K41" s="227"/>
+      <c r="L41" s="227"/>
+      <c r="M41" s="227"/>
+      <c r="N41" s="227"/>
+      <c r="O41" s="227"/>
+      <c r="P41" s="228"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="241" t="s">
+        <v>518</v>
+      </c>
+      <c r="B42" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C42" s="242" t="s">
+        <v>397</v>
+      </c>
+      <c r="D42" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E42" s="243" t="s">
+        <v>519</v>
+      </c>
+      <c r="F42" s="227"/>
+      <c r="G42" s="227"/>
+      <c r="H42" s="227"/>
+      <c r="I42" s="227"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="227"/>
+      <c r="L42" s="227"/>
+      <c r="M42" s="227"/>
+      <c r="N42" s="227"/>
+      <c r="O42" s="227"/>
+      <c r="P42" s="228"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F43" s="227"/>
+      <c r="G43" s="227"/>
+      <c r="H43" s="227"/>
+      <c r="I43" s="227"/>
+      <c r="J43" s="227"/>
+      <c r="K43" s="227"/>
+      <c r="L43" s="227"/>
+      <c r="M43" s="227"/>
+      <c r="N43" s="227"/>
+      <c r="O43" s="227"/>
+      <c r="P43" s="228"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="234" t="s">
+        <v>679</v>
+      </c>
+      <c r="F44" s="227"/>
+      <c r="G44" s="227"/>
+      <c r="H44" s="227"/>
+      <c r="I44" s="227"/>
+      <c r="J44" s="227"/>
+      <c r="K44" s="227"/>
+      <c r="L44" s="227"/>
+      <c r="M44" s="227"/>
+      <c r="N44" s="227"/>
+      <c r="O44" s="227"/>
+      <c r="P44" s="228"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="234" t="s">
+        <v>680</v>
+      </c>
+      <c r="F45" s="227"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="227"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+      <c r="M45" s="227"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="227"/>
+      <c r="P45" s="228"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="234" t="s">
+        <v>681</v>
+      </c>
+      <c r="F46" s="227"/>
+      <c r="G46" s="227"/>
+      <c r="H46" s="227"/>
+      <c r="I46" s="227"/>
+      <c r="J46" s="227"/>
+      <c r="K46" s="227"/>
+      <c r="L46" s="227"/>
+      <c r="M46" s="227"/>
+      <c r="N46" s="227"/>
+      <c r="O46" s="227"/>
+      <c r="P46" s="228"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="234" t="s">
+        <v>682</v>
+      </c>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="227"/>
+      <c r="I47" s="227"/>
+      <c r="J47" s="227"/>
+      <c r="K47" s="227"/>
+      <c r="L47" s="227"/>
+      <c r="M47" s="227"/>
+      <c r="N47" s="227"/>
+      <c r="O47" s="227"/>
+      <c r="P47" s="228"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="234" t="s">
+        <v>683</v>
+      </c>
+      <c r="F48" s="227"/>
+      <c r="G48" s="227"/>
+      <c r="H48" s="227"/>
+      <c r="I48" s="227"/>
+      <c r="J48" s="227"/>
+      <c r="K48" s="227"/>
+      <c r="L48" s="227"/>
+      <c r="M48" s="227"/>
+      <c r="N48" s="227"/>
+      <c r="O48" s="227"/>
+      <c r="P48" s="228"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F49" s="227"/>
+      <c r="G49" s="227"/>
+      <c r="H49" s="227"/>
+      <c r="I49" s="227"/>
+      <c r="J49" s="227"/>
+      <c r="K49" s="227"/>
+      <c r="L49" s="227"/>
+      <c r="M49" s="227"/>
+      <c r="N49" s="227"/>
+      <c r="O49" s="227"/>
+      <c r="P49" s="228"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F50" s="227"/>
+      <c r="G50" s="227"/>
+      <c r="H50" s="227"/>
+      <c r="I50" s="227"/>
+      <c r="J50" s="227"/>
+      <c r="K50" s="227"/>
+      <c r="L50" s="227"/>
+      <c r="M50" s="227"/>
+      <c r="N50" s="227"/>
+      <c r="O50" s="227"/>
+      <c r="P50" s="228"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="232" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="233" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="233" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" s="233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" s="232" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="227"/>
+      <c r="G51" s="227"/>
+      <c r="H51" s="227"/>
+      <c r="I51" s="227"/>
+      <c r="J51" s="227"/>
+      <c r="K51" s="227"/>
+      <c r="L51" s="227"/>
+      <c r="M51" s="227"/>
+      <c r="N51" s="227"/>
+      <c r="O51" s="227"/>
+      <c r="P51" s="228"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="229"/>
+      <c r="B52" s="239"/>
+      <c r="C52" s="239"/>
+      <c r="D52" s="239"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="227"/>
+      <c r="G52" s="227"/>
+      <c r="H52" s="227"/>
+      <c r="I52" s="227"/>
+      <c r="J52" s="227"/>
+      <c r="K52" s="227"/>
+      <c r="L52" s="227"/>
+      <c r="M52" s="227"/>
+      <c r="N52" s="227"/>
+      <c r="O52" s="227"/>
+      <c r="P52" s="228"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="238" t="s">
+        <v>584</v>
+      </c>
+      <c r="B53" s="238"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="227"/>
+      <c r="G53" s="227"/>
+      <c r="H53" s="227"/>
+      <c r="I53" s="227"/>
+      <c r="J53" s="227"/>
+      <c r="K53" s="227"/>
+      <c r="L53" s="227"/>
+      <c r="M53" s="227"/>
+      <c r="N53" s="227"/>
+      <c r="O53" s="227"/>
+      <c r="P53" s="228"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="234" t="s">
+        <v>415</v>
+      </c>
+      <c r="B54" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C54" s="235" t="s">
+        <v>397</v>
+      </c>
+      <c r="D54" s="235">
+        <v>1</v>
+      </c>
+      <c r="E54" s="236" t="s">
+        <v>416</v>
+      </c>
+      <c r="F54" s="227"/>
+      <c r="G54" s="227"/>
+      <c r="H54" s="227"/>
+      <c r="I54" s="227"/>
+      <c r="J54" s="227"/>
+      <c r="K54" s="227"/>
+      <c r="L54" s="227"/>
+      <c r="M54" s="227"/>
+      <c r="N54" s="227"/>
+      <c r="O54" s="227"/>
+      <c r="P54" s="228"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="241" t="s">
+        <v>447</v>
+      </c>
+      <c r="B55" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C55" s="242" t="s">
+        <v>448</v>
+      </c>
+      <c r="D55" s="242">
+        <v>1</v>
+      </c>
+      <c r="E55" s="243" t="s">
+        <v>449</v>
+      </c>
+      <c r="F55" s="227"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="227"/>
+      <c r="I55" s="227"/>
+      <c r="J55" s="227"/>
+      <c r="K55" s="227"/>
+      <c r="L55" s="227"/>
+      <c r="M55" s="227"/>
+      <c r="N55" s="227"/>
+      <c r="O55" s="227"/>
+      <c r="P55" s="228"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="234" t="s">
+        <v>477</v>
+      </c>
+      <c r="B56" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C56" s="235" t="s">
+        <v>436</v>
+      </c>
+      <c r="D56" s="235">
+        <v>2</v>
+      </c>
+      <c r="E56" s="236" t="s">
+        <v>478</v>
+      </c>
+      <c r="F56" s="227"/>
+      <c r="G56" s="227"/>
+      <c r="H56" s="227"/>
+      <c r="I56" s="227"/>
+      <c r="J56" s="227"/>
+      <c r="K56" s="227"/>
+      <c r="L56" s="227"/>
+      <c r="M56" s="227"/>
+      <c r="N56" s="227"/>
+      <c r="O56" s="227"/>
+      <c r="P56" s="228"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="241" t="s">
+        <v>506</v>
+      </c>
+      <c r="B57" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C57" s="242" t="s">
+        <v>314</v>
+      </c>
+      <c r="D57" s="242">
+        <v>3</v>
+      </c>
+      <c r="E57" s="243" t="s">
+        <v>507</v>
+      </c>
+      <c r="F57" s="227"/>
+      <c r="G57" s="227"/>
+      <c r="H57" s="227"/>
+      <c r="I57" s="227"/>
+      <c r="J57" s="227"/>
+      <c r="K57" s="227"/>
+      <c r="L57" s="227"/>
+      <c r="M57" s="227"/>
+      <c r="N57" s="227"/>
+      <c r="O57" s="227"/>
+      <c r="P57" s="228"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="234" t="s">
+        <v>417</v>
+      </c>
+      <c r="B58" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C58" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D58" s="235">
+        <v>2</v>
+      </c>
+      <c r="E58" s="236" t="s">
+        <v>418</v>
+      </c>
+      <c r="F58" s="227"/>
+      <c r="G58" s="227"/>
+      <c r="H58" s="227"/>
+      <c r="I58" s="227"/>
+      <c r="J58" s="227"/>
+      <c r="K58" s="227"/>
+      <c r="L58" s="227"/>
+      <c r="M58" s="227"/>
+      <c r="N58" s="227"/>
+      <c r="O58" s="227"/>
+      <c r="P58" s="228"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="241" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C59" s="242" t="s">
+        <v>448</v>
+      </c>
+      <c r="D59" s="242">
+        <v>2</v>
+      </c>
+      <c r="E59" s="243" t="s">
+        <v>480</v>
+      </c>
+      <c r="F59" s="227"/>
+      <c r="G59" s="227"/>
+      <c r="H59" s="227"/>
+      <c r="I59" s="227"/>
+      <c r="J59" s="227"/>
+      <c r="K59" s="227"/>
+      <c r="L59" s="227"/>
+      <c r="M59" s="227"/>
+      <c r="N59" s="227"/>
+      <c r="O59" s="227"/>
+      <c r="P59" s="228"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="234" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C60" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D60" s="235">
+        <v>2</v>
+      </c>
+      <c r="E60" s="236" t="s">
+        <v>450</v>
+      </c>
+      <c r="F60" s="227"/>
+      <c r="G60" s="227"/>
+      <c r="H60" s="227"/>
+      <c r="I60" s="227"/>
+      <c r="J60" s="227"/>
+      <c r="K60" s="227"/>
+      <c r="L60" s="227"/>
+      <c r="M60" s="227"/>
+      <c r="N60" s="227"/>
+      <c r="O60" s="227"/>
+      <c r="P60" s="228"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="241" t="s">
+        <v>481</v>
+      </c>
+      <c r="B61" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C61" s="242" t="s">
+        <v>448</v>
+      </c>
+      <c r="D61" s="242">
+        <v>2</v>
+      </c>
+      <c r="E61" s="243" t="s">
+        <v>450</v>
+      </c>
+      <c r="F61" s="227"/>
+      <c r="G61" s="227"/>
+      <c r="H61" s="227"/>
+      <c r="I61" s="227"/>
+      <c r="J61" s="227"/>
+      <c r="K61" s="227"/>
+      <c r="L61" s="227"/>
+      <c r="M61" s="227"/>
+      <c r="N61" s="227"/>
+      <c r="O61" s="227"/>
+      <c r="P61" s="228"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="234" t="s">
+        <v>419</v>
+      </c>
+      <c r="B62" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C62" s="235" t="s">
+        <v>420</v>
+      </c>
+      <c r="D62" s="235">
+        <v>2</v>
+      </c>
+      <c r="E62" s="236" t="s">
+        <v>421</v>
+      </c>
+      <c r="F62" s="227"/>
+      <c r="G62" s="227"/>
+      <c r="H62" s="227"/>
+      <c r="I62" s="227"/>
+      <c r="J62" s="227"/>
+      <c r="K62" s="227"/>
+      <c r="L62" s="227"/>
+      <c r="M62" s="227"/>
+      <c r="N62" s="227"/>
+      <c r="O62" s="227"/>
+      <c r="P62" s="228"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="241" t="s">
+        <v>508</v>
+      </c>
+      <c r="B63" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C63" s="242" t="s">
+        <v>448</v>
+      </c>
+      <c r="D63" s="242">
+        <v>3</v>
+      </c>
+      <c r="E63" s="243" t="s">
+        <v>507</v>
+      </c>
+      <c r="F63" s="227"/>
+      <c r="G63" s="227"/>
+      <c r="H63" s="227"/>
+      <c r="I63" s="227"/>
+      <c r="J63" s="227"/>
+      <c r="K63" s="227"/>
+      <c r="L63" s="227"/>
+      <c r="M63" s="227"/>
+      <c r="N63" s="227"/>
+      <c r="O63" s="227"/>
+      <c r="P63" s="228"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="234" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C64" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D64" s="235">
+        <v>1</v>
+      </c>
+      <c r="E64" s="236" t="s">
+        <v>422</v>
+      </c>
+      <c r="F64" s="227"/>
+      <c r="G64" s="227"/>
+      <c r="H64" s="227"/>
+      <c r="I64" s="227"/>
+      <c r="J64" s="227"/>
+      <c r="K64" s="227"/>
+      <c r="L64" s="227"/>
+      <c r="M64" s="227"/>
+      <c r="N64" s="227"/>
+      <c r="O64" s="227"/>
+      <c r="P64" s="228"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="241" t="s">
+        <v>451</v>
+      </c>
+      <c r="B65" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C65" s="242" t="s">
+        <v>313</v>
+      </c>
+      <c r="D65" s="242">
+        <v>1</v>
+      </c>
+      <c r="E65" s="243" t="s">
+        <v>452</v>
+      </c>
+      <c r="F65" s="227"/>
+      <c r="G65" s="227"/>
+      <c r="H65" s="227"/>
+      <c r="I65" s="227"/>
+      <c r="J65" s="227"/>
+      <c r="K65" s="227"/>
+      <c r="L65" s="227"/>
+      <c r="M65" s="227"/>
+      <c r="N65" s="227"/>
+      <c r="O65" s="227"/>
+      <c r="P65" s="228"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="234" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C66" s="235" t="s">
+        <v>425</v>
+      </c>
+      <c r="D66" s="235">
+        <v>2</v>
+      </c>
+      <c r="E66" s="236" t="s">
+        <v>482</v>
+      </c>
+      <c r="F66" s="227"/>
+      <c r="G66" s="227"/>
+      <c r="H66" s="227"/>
+      <c r="I66" s="227"/>
+      <c r="J66" s="227"/>
+      <c r="K66" s="227"/>
+      <c r="L66" s="227"/>
+      <c r="M66" s="227"/>
+      <c r="N66" s="227"/>
+      <c r="O66" s="227"/>
+      <c r="P66" s="228"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="241" t="s">
+        <v>483</v>
+      </c>
+      <c r="B67" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C67" s="242" t="s">
+        <v>315</v>
+      </c>
+      <c r="D67" s="242">
+        <v>2</v>
+      </c>
+      <c r="E67" s="243" t="s">
+        <v>602</v>
+      </c>
+      <c r="F67" s="227"/>
+      <c r="G67" s="227"/>
+      <c r="H67" s="227"/>
+      <c r="I67" s="227"/>
+      <c r="J67" s="227"/>
+      <c r="K67" s="227"/>
+      <c r="L67" s="227"/>
+      <c r="M67" s="227"/>
+      <c r="N67" s="227"/>
+      <c r="O67" s="227"/>
+      <c r="P67" s="228"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="234" t="s">
+        <v>509</v>
+      </c>
+      <c r="B68" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C68" s="235" t="s">
+        <v>292</v>
+      </c>
+      <c r="D68" s="235">
+        <v>3</v>
+      </c>
+      <c r="E68" s="236" t="s">
+        <v>603</v>
+      </c>
+      <c r="F68" s="237"/>
+      <c r="G68" s="237"/>
+      <c r="H68" s="237"/>
+      <c r="I68" s="237"/>
+      <c r="J68" s="237"/>
+      <c r="K68" s="237"/>
+      <c r="L68" s="237"/>
+      <c r="M68" s="237"/>
+      <c r="N68" s="237"/>
+      <c r="O68" s="237"/>
+      <c r="P68" s="237"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" s="241" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C69" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D69" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E69" s="243" t="s">
+        <v>423</v>
+      </c>
+      <c r="F69" s="237"/>
+      <c r="G69" s="237"/>
+      <c r="H69" s="237"/>
+      <c r="I69" s="237"/>
+      <c r="J69" s="237"/>
+      <c r="K69" s="237"/>
+      <c r="L69" s="237"/>
+      <c r="M69" s="237"/>
+      <c r="N69" s="237"/>
+      <c r="O69" s="237"/>
+      <c r="P69" s="237"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="234" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C70" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D70" s="235">
+        <v>1</v>
+      </c>
+      <c r="E70" s="236" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="241" t="s">
+        <v>475</v>
+      </c>
+      <c r="B71" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C71" s="242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D71" s="242">
+        <v>1</v>
+      </c>
+      <c r="E71" s="243" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" s="234" t="s">
+        <v>281</v>
+      </c>
+      <c r="B72" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C72" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72" s="235">
+        <v>1</v>
+      </c>
+      <c r="E72" s="236" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="241" t="s">
+        <v>453</v>
+      </c>
+      <c r="B73" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" s="242" t="s">
+        <v>314</v>
+      </c>
+      <c r="D73" s="242">
+        <v>2</v>
+      </c>
+      <c r="E73" s="243" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="234" t="s">
+        <v>455</v>
+      </c>
+      <c r="B74" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="235" t="s">
+        <v>456</v>
+      </c>
+      <c r="D74" s="235">
+        <v>2</v>
+      </c>
+      <c r="E74" s="236" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" s="241" t="s">
+        <v>484</v>
+      </c>
+      <c r="B75" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C75" s="242" t="s">
+        <v>315</v>
+      </c>
+      <c r="D75" s="242">
+        <v>2</v>
+      </c>
+      <c r="E75" s="243" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="234" t="s">
+        <v>486</v>
+      </c>
+      <c r="B76" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C76" s="235" t="s">
+        <v>425</v>
+      </c>
+      <c r="D76" s="235">
+        <v>3</v>
+      </c>
+      <c r="E76" s="236" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" s="241" t="s">
+        <v>510</v>
+      </c>
+      <c r="B77" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C77" s="242" t="s">
+        <v>511</v>
+      </c>
+      <c r="D77" s="242">
+        <v>3</v>
+      </c>
+      <c r="E77" s="243" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" s="234" t="s">
+        <v>513</v>
+      </c>
+      <c r="B78" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C78" s="235" t="s">
+        <v>514</v>
+      </c>
+      <c r="D78" s="235">
+        <v>4</v>
+      </c>
+      <c r="E78" s="236" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" s="241" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C79" s="242" t="s">
+        <v>436</v>
+      </c>
+      <c r="D79" s="242">
+        <v>1</v>
+      </c>
+      <c r="E79" s="243" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="234" t="s">
+        <v>488</v>
+      </c>
+      <c r="B80" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C80" s="235" t="s">
+        <v>436</v>
+      </c>
+      <c r="D80" s="235">
+        <v>1</v>
+      </c>
+      <c r="E80" s="236" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="238" t="s">
+        <v>596</v>
+      </c>
+      <c r="B82" s="238"/>
+      <c r="C82" s="238"/>
+      <c r="D82" s="238"/>
+      <c r="E82" s="238"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="234" t="s">
+        <v>548</v>
+      </c>
+      <c r="B83" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C83" s="235" t="s">
+        <v>549</v>
+      </c>
+      <c r="D83" s="235">
+        <v>1</v>
+      </c>
+      <c r="E83" s="236" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="241" t="s">
+        <v>551</v>
+      </c>
+      <c r="B84" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C84" s="242" t="s">
+        <v>552</v>
+      </c>
+      <c r="D84" s="242">
+        <v>2</v>
+      </c>
+      <c r="E84" s="243" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="234" t="s">
+        <v>554</v>
+      </c>
+      <c r="B85" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C85" s="235" t="s">
+        <v>549</v>
+      </c>
+      <c r="D85" s="235">
+        <v>2</v>
+      </c>
+      <c r="E85" s="236" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="241" t="s">
+        <v>556</v>
+      </c>
+      <c r="B86" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C86" s="242" t="s">
+        <v>552</v>
+      </c>
+      <c r="D86" s="242">
+        <v>2</v>
+      </c>
+      <c r="E86" s="243" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="234" t="s">
+        <v>557</v>
+      </c>
+      <c r="B87" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C87" s="235" t="s">
+        <v>558</v>
+      </c>
+      <c r="D87" s="235">
+        <v>1</v>
+      </c>
+      <c r="E87" s="236" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="241" t="s">
+        <v>560</v>
+      </c>
+      <c r="B88" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C88" s="242" t="s">
+        <v>561</v>
+      </c>
+      <c r="D88" s="242">
+        <v>1</v>
+      </c>
+      <c r="E88" s="243" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="234" t="s">
+        <v>563</v>
+      </c>
+      <c r="B89" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C89" s="235" t="s">
+        <v>524</v>
+      </c>
+      <c r="D89" s="235">
+        <v>1</v>
+      </c>
+      <c r="E89" s="236" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="241" t="s">
+        <v>565</v>
+      </c>
+      <c r="B90" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C90" s="242" t="s">
+        <v>552</v>
+      </c>
+      <c r="D90" s="242">
+        <v>2</v>
+      </c>
+      <c r="E90" s="243" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="234" t="s">
+        <v>566</v>
+      </c>
+      <c r="B91" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C91" s="235" t="s">
+        <v>567</v>
+      </c>
+      <c r="D91" s="235">
+        <v>3</v>
+      </c>
+      <c r="E91" s="236" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="241" t="s">
+        <v>568</v>
+      </c>
+      <c r="B92" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C92" s="242" t="s">
+        <v>549</v>
+      </c>
+      <c r="D92" s="242">
+        <v>1</v>
+      </c>
+      <c r="E92" s="243" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="234" t="s">
+        <v>570</v>
+      </c>
+      <c r="B93" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C93" s="235" t="s">
+        <v>571</v>
+      </c>
+      <c r="D93" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E93" s="236" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="241" t="s">
+        <v>573</v>
+      </c>
+      <c r="B94" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C94" s="242" t="s">
+        <v>561</v>
+      </c>
+      <c r="D94" s="242">
+        <v>1</v>
+      </c>
+      <c r="E94" s="243" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="234" t="s">
+        <v>575</v>
+      </c>
+      <c r="B95" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C95" s="235" t="s">
+        <v>561</v>
+      </c>
+      <c r="D95" s="235">
+        <v>1</v>
+      </c>
+      <c r="E95" s="236" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="241" t="s">
+        <v>577</v>
+      </c>
+      <c r="B96" s="244" t="s">
+        <v>597</v>
+      </c>
+      <c r="C96" s="242" t="s">
+        <v>552</v>
+      </c>
+      <c r="D96" s="242">
+        <v>1</v>
+      </c>
+      <c r="E96" s="243" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="234" t="s">
+        <v>579</v>
+      </c>
+      <c r="B97" s="240" t="s">
+        <v>597</v>
+      </c>
+      <c r="C97" s="235" t="s">
+        <v>580</v>
+      </c>
+      <c r="D97" s="235">
+        <v>1</v>
+      </c>
+      <c r="E97" s="236" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="232" t="s">
+        <v>45</v>
+      </c>
+      <c r="B104" s="233" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" s="233" t="s">
+        <v>262</v>
+      </c>
+      <c r="D104" s="233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E104" s="232" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="229"/>
+      <c r="B105" s="239"/>
+      <c r="C105" s="239"/>
+      <c r="D105" s="239"/>
+      <c r="E105" s="229"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="238" t="s">
+        <v>587</v>
+      </c>
+      <c r="B106" s="238"/>
+      <c r="C106" s="238"/>
+      <c r="D106" s="238"/>
+      <c r="E106" s="238"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="234" t="s">
+        <v>410</v>
+      </c>
+      <c r="B107" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C107" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D107" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E107" s="236" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="241" t="s">
+        <v>471</v>
+      </c>
+      <c r="B108" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C108" s="242" t="s">
+        <v>313</v>
+      </c>
+      <c r="D108" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E108" s="243" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="234" t="s">
+        <v>277</v>
+      </c>
+      <c r="B109" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C109" s="235" t="s">
+        <v>313</v>
+      </c>
+      <c r="D109" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E109" s="236" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="241" t="s">
+        <v>412</v>
+      </c>
+      <c r="B110" s="244" t="s">
+        <v>375</v>
+      </c>
+      <c r="C110" s="242" t="s">
+        <v>268</v>
+      </c>
+      <c r="D110" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E110" s="243" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="234" t="s">
+        <v>406</v>
+      </c>
+      <c r="B111" s="240" t="s">
+        <v>375</v>
+      </c>
+      <c r="C111" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" s="235">
+        <v>1</v>
+      </c>
+      <c r="E111" s="236" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="241" t="s">
+        <v>605</v>
+      </c>
+      <c r="B112" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C112" s="242" t="s">
+        <v>315</v>
+      </c>
+      <c r="D112" s="242">
+        <v>1</v>
+      </c>
+      <c r="E112" s="243" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="234" t="s">
+        <v>607</v>
+      </c>
+      <c r="B113" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C113" s="235" t="s">
+        <v>270</v>
+      </c>
+      <c r="D113" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E113" s="236" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="241" t="s">
+        <v>609</v>
+      </c>
+      <c r="B114" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C114" s="242" t="s">
+        <v>397</v>
+      </c>
+      <c r="D114" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E114" s="243" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="234" t="s">
+        <v>611</v>
+      </c>
+      <c r="B115" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C115" s="235" t="s">
+        <v>314</v>
+      </c>
+      <c r="D115" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E115" s="236" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="241" t="s">
+        <v>613</v>
+      </c>
+      <c r="B116" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C116" s="242" t="s">
+        <v>272</v>
+      </c>
+      <c r="D116" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E116" s="243" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="234" t="s">
+        <v>615</v>
+      </c>
+      <c r="B117" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C117" s="235" t="s">
+        <v>313</v>
+      </c>
+      <c r="D117" s="235">
+        <v>1</v>
+      </c>
+      <c r="E117" s="236" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A118" s="241" t="s">
+        <v>617</v>
+      </c>
+      <c r="B118" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C118" s="242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D118" s="242">
+        <v>1</v>
+      </c>
+      <c r="E118" s="243" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A119" s="234" t="s">
+        <v>647</v>
+      </c>
+      <c r="B119" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C119" s="235" t="s">
+        <v>314</v>
+      </c>
+      <c r="D119" s="235">
+        <v>1</v>
+      </c>
+      <c r="E119" s="236" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="241" t="s">
+        <v>649</v>
+      </c>
+      <c r="B120" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C120" s="242" t="s">
+        <v>272</v>
+      </c>
+      <c r="D120" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E120" s="243" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="234" t="s">
+        <v>651</v>
+      </c>
+      <c r="B121" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C121" s="235" t="s">
+        <v>315</v>
+      </c>
+      <c r="D121" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E121" s="236" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="241" t="s">
+        <v>299</v>
+      </c>
+      <c r="B122" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C122" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D122" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E122" s="243" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="234" t="s">
+        <v>301</v>
+      </c>
+      <c r="B123" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C123" s="235" t="s">
+        <v>292</v>
+      </c>
+      <c r="D123" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E123" s="236" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A124" s="241" t="s">
+        <v>300</v>
+      </c>
+      <c r="B124" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C124" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D124" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E124" s="243" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="234" t="s">
+        <v>502</v>
+      </c>
+      <c r="B125" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C125" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D125" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E125" s="236" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A126" s="241" t="s">
+        <v>619</v>
+      </c>
+      <c r="B126" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C126" s="242" t="s">
+        <v>292</v>
+      </c>
+      <c r="D126" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E126" s="243" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="234" t="s">
+        <v>625</v>
+      </c>
+      <c r="B127" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C127" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D127" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E127" s="236" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="241" t="s">
+        <v>623</v>
+      </c>
+      <c r="B128" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C128" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D128" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E128" s="243" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A129" s="234" t="s">
+        <v>620</v>
+      </c>
+      <c r="B129" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C129" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D129" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E129" s="236" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A130" s="241" t="s">
+        <v>547</v>
+      </c>
+      <c r="B130" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C130" s="242" t="s">
+        <v>289</v>
+      </c>
+      <c r="D130" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E130" s="243" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="234" t="s">
+        <v>542</v>
+      </c>
+      <c r="B131" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C131" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D131" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E131" s="236" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="241" t="s">
+        <v>629</v>
+      </c>
+      <c r="B132" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C132" s="242" t="s">
+        <v>285</v>
+      </c>
+      <c r="D132" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E132" s="243" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="234" t="s">
+        <v>627</v>
+      </c>
+      <c r="B133" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C133" s="235" t="s">
+        <v>285</v>
+      </c>
+      <c r="D133" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E133" s="236" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="241" t="s">
+        <v>631</v>
+      </c>
+      <c r="B134" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C134" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D134" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E134" s="243" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="234" t="s">
+        <v>588</v>
+      </c>
+      <c r="B135" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C135" s="235" t="s">
+        <v>292</v>
+      </c>
+      <c r="D135" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E135" s="236" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="241" t="s">
+        <v>633</v>
+      </c>
+      <c r="B136" s="244" t="s">
+        <v>377</v>
+      </c>
+      <c r="C136" s="242" t="s">
+        <v>436</v>
+      </c>
+      <c r="D136" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E136" s="243" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="234" t="s">
+        <v>590</v>
+      </c>
+      <c r="B137" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C137" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D137" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E137" s="236" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="241" t="s">
+        <v>635</v>
+      </c>
+      <c r="B138" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C138" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D138" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E138" s="243" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="234" t="s">
+        <v>592</v>
+      </c>
+      <c r="B139" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C139" s="235" t="s">
+        <v>283</v>
+      </c>
+      <c r="D139" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E139" s="236" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="241" t="s">
+        <v>640</v>
+      </c>
+      <c r="B140" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C140" s="242" t="s">
+        <v>436</v>
+      </c>
+      <c r="D140" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E140" s="243" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="234" t="s">
+        <v>638</v>
+      </c>
+      <c r="B141" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C141" s="235" t="s">
+        <v>456</v>
+      </c>
+      <c r="D141" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E141" s="236" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A142" s="241" t="s">
+        <v>594</v>
+      </c>
+      <c r="B142" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C142" s="242" t="s">
+        <v>558</v>
+      </c>
+      <c r="D142" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E142" s="243" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="234" t="s">
+        <v>642</v>
+      </c>
+      <c r="B143" s="240" t="s">
+        <v>377</v>
+      </c>
+      <c r="C143" s="235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D143" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E143" s="236" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="232" t="s">
+        <v>45</v>
+      </c>
+      <c r="B148" s="233" t="s">
+        <v>44</v>
+      </c>
+      <c r="C148" s="233" t="s">
+        <v>262</v>
+      </c>
+      <c r="D148" s="233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E148" s="232" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" s="236" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="229"/>
+      <c r="B149" s="239"/>
+      <c r="C149" s="239"/>
+      <c r="D149" s="239"/>
+      <c r="E149" s="229"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="238" t="s">
+        <v>595</v>
+      </c>
+      <c r="B150" s="238"/>
+      <c r="C150" s="238"/>
+      <c r="D150" s="238"/>
+      <c r="E150" s="238"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="234" t="s">
+        <v>492</v>
+      </c>
+      <c r="B151" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C151" s="235" t="s">
+        <v>285</v>
+      </c>
+      <c r="D151" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E151" s="236" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="241" t="s">
+        <v>520</v>
+      </c>
+      <c r="B152" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C152" s="242" t="s">
+        <v>521</v>
+      </c>
+      <c r="D152" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E152" s="243" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="234" t="s">
+        <v>494</v>
+      </c>
+      <c r="B153" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C153" s="235" t="s">
+        <v>283</v>
+      </c>
+      <c r="D153" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E153" s="236" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A154" s="241" t="s">
+        <v>286</v>
+      </c>
+      <c r="B154" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C154" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D154" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E154" s="243" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A155" s="234" t="s">
+        <v>288</v>
+      </c>
+      <c r="B155" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C155" s="235" t="s">
+        <v>524</v>
+      </c>
+      <c r="D155" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E155" s="236" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A156" s="241" t="s">
+        <v>526</v>
+      </c>
+      <c r="B156" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C156" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D156" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E156" s="243" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="234" t="s">
+        <v>306</v>
+      </c>
+      <c r="B157" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C157" s="235" t="s">
+        <v>524</v>
+      </c>
+      <c r="D157" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E157" s="236" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A158" s="241" t="s">
+        <v>290</v>
+      </c>
+      <c r="B158" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C158" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D158" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E158" s="243" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A159" s="234" t="s">
+        <v>530</v>
+      </c>
+      <c r="B159" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C159" s="235" t="s">
+        <v>531</v>
+      </c>
+      <c r="D159" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E159" s="236" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="241" t="s">
+        <v>533</v>
+      </c>
+      <c r="B160" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C160" s="242" t="s">
+        <v>534</v>
+      </c>
+      <c r="D160" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E160" s="243" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="234" t="s">
+        <v>653</v>
+      </c>
+      <c r="B161" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C161" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D161" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E161" s="236" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A162" s="241" t="s">
+        <v>655</v>
+      </c>
+      <c r="B162" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C162" s="242" t="s">
+        <v>531</v>
+      </c>
+      <c r="D162" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E162" s="243" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="234" t="s">
+        <v>657</v>
+      </c>
+      <c r="B163" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C163" s="235" t="s">
+        <v>308</v>
+      </c>
+      <c r="D163" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E163" s="236" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="241" t="s">
+        <v>659</v>
+      </c>
+      <c r="B164" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C164" s="242" t="s">
+        <v>285</v>
+      </c>
+      <c r="D164" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E164" s="243" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="234" t="s">
+        <v>661</v>
+      </c>
+      <c r="B165" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C165" s="235" t="s">
+        <v>285</v>
+      </c>
+      <c r="D165" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E165" s="236" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="241" t="s">
+        <v>663</v>
+      </c>
+      <c r="B166" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C166" s="242" t="s">
+        <v>287</v>
+      </c>
+      <c r="D166" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E166" s="243" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="234" t="s">
+        <v>665</v>
+      </c>
+      <c r="B167" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C167" s="235" t="s">
+        <v>292</v>
+      </c>
+      <c r="D167" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E167" s="236" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="241" t="s">
+        <v>291</v>
+      </c>
+      <c r="B168" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C168" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D168" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E168" s="243" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A169" s="234" t="s">
+        <v>293</v>
+      </c>
+      <c r="B169" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C169" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D169" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E169" s="236" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="241" t="s">
+        <v>498</v>
+      </c>
+      <c r="B170" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C170" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D170" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E170" s="243" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="234" t="s">
+        <v>500</v>
+      </c>
+      <c r="B171" s="240" t="s">
+        <v>583</v>
+      </c>
+      <c r="C171" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D171" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E171" s="236" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="241" t="s">
+        <v>667</v>
+      </c>
+      <c r="B172" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C172" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="D172" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E172" s="243" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="234" t="s">
+        <v>669</v>
+      </c>
+      <c r="B173" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C173" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D173" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E173" s="236" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A174" s="241" t="s">
+        <v>294</v>
+      </c>
+      <c r="B174" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C174" s="242" t="s">
+        <v>289</v>
+      </c>
+      <c r="D174" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E174" s="243" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="234" t="s">
+        <v>296</v>
+      </c>
+      <c r="B175" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C175" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D175" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E175" s="236" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="241" t="s">
+        <v>538</v>
+      </c>
+      <c r="B176" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C176" s="242" t="s">
+        <v>289</v>
+      </c>
+      <c r="D176" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E176" s="243" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A177" s="234" t="s">
+        <v>540</v>
+      </c>
+      <c r="B177" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C177" s="235" t="s">
+        <v>289</v>
+      </c>
+      <c r="D177" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E177" s="236" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A178" s="241" t="s">
+        <v>543</v>
+      </c>
+      <c r="B178" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C178" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D178" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E178" s="243" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A179" s="234" t="s">
+        <v>297</v>
+      </c>
+      <c r="B179" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C179" s="235" t="s">
+        <v>308</v>
+      </c>
+      <c r="D179" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E179" s="236" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="241" t="s">
+        <v>298</v>
+      </c>
+      <c r="B180" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C180" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D180" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E180" s="243" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A181" s="234" t="s">
+        <v>671</v>
+      </c>
+      <c r="B181" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C181" s="235" t="s">
+        <v>308</v>
+      </c>
+      <c r="D181" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E181" s="236" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A182" s="241" t="s">
+        <v>673</v>
+      </c>
+      <c r="B182" s="244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C182" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="D182" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E182" s="243" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="234" t="s">
+        <v>675</v>
+      </c>
+      <c r="B183" s="240" t="s">
+        <v>585</v>
+      </c>
+      <c r="C183" s="235" t="s">
+        <v>295</v>
+      </c>
+      <c r="D183" s="235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E183" s="236" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A184" s="241" t="s">
+        <v>677</v>
+      </c>
+      <c r="B184" s="244" t="s">
+        <v>583</v>
+      </c>
+      <c r="C184" s="242" t="s">
+        <v>313</v>
+      </c>
+      <c r="D184" s="242" t="s">
+        <v>329</v>
+      </c>
+      <c r="E184" s="243" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" s="236" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="234"/>
+      <c r="B185" s="240"/>
+      <c r="C185" s="235"/>
+      <c r="D185" s="235"/>
+    </row>
+    <row r="186" spans="1:11" s="236" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="234"/>
+      <c r="B186" s="240"/>
+      <c r="C186" s="235"/>
+      <c r="D186" s="235"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A188" s="230" t="s">
         <v>356</v>
       </c>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="F25" s="173" t="s">
-        <v>357</v>
-      </c>
-      <c r="G25" s="174"/>
-      <c r="H25" s="174"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="174"/>
-      <c r="K25" s="174"/>
-      <c r="L25" s="174"/>
-      <c r="M25" s="174"/>
-      <c r="N25" s="174"/>
-      <c r="O25" s="174"/>
-      <c r="P25" s="175" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="169"/>
-      <c r="B26" s="170"/>
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="172"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="171"/>
-      <c r="B36" s="171"/>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="166"/>
-      <c r="C37" s="166"/>
-      <c r="D37" s="166"/>
-      <c r="E37" s="166"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="171"/>
-      <c r="B38" s="171"/>
-      <c r="C38" s="171"/>
-      <c r="D38" s="171"/>
-      <c r="E38" s="171"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="166"/>
-      <c r="C39" s="166"/>
-      <c r="D39" s="166"/>
-      <c r="E39" s="166"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="171"/>
-      <c r="B40" s="171"/>
-      <c r="C40" s="171"/>
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
+      <c r="B188" s="230"/>
+      <c r="C188" s="230"/>
+      <c r="D188" s="230"/>
+      <c r="E188" s="230"/>
+      <c r="F188" s="239"/>
+      <c r="G188" s="239"/>
+      <c r="H188" s="239"/>
+      <c r="I188" s="239"/>
+      <c r="J188" s="239"/>
+      <c r="K188" s="239"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A190" s="245"/>
+      <c r="B190" s="246"/>
+      <c r="C190" s="247"/>
+      <c r="D190" s="247"/>
+      <c r="E190" s="248"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A192" s="245"/>
+      <c r="B192" s="246"/>
+      <c r="C192" s="247"/>
+      <c r="D192" s="247"/>
+      <c r="E192" s="248"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="245"/>
+      <c r="B194" s="246"/>
+      <c r="C194" s="247"/>
+      <c r="D194" s="247"/>
+      <c r="E194" s="248"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" s="245"/>
+      <c r="B196" s="246"/>
+      <c r="C196" s="247"/>
+      <c r="D196" s="247"/>
+      <c r="E196" s="248"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" s="245"/>
+      <c r="B198" s="246"/>
+      <c r="C198" s="247"/>
+      <c r="D198" s="247"/>
+      <c r="E198" s="248"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="245"/>
+      <c r="B200" s="246"/>
+      <c r="C200" s="247"/>
+      <c r="D200" s="247"/>
+      <c r="E200" s="248"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="245"/>
+      <c r="B202" s="246"/>
+      <c r="C202" s="247"/>
+      <c r="D202" s="247"/>
+      <c r="E202" s="248"/>
+    </row>
+    <row r="234" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F234" s="236"/>
+      <c r="G234" s="236"/>
+      <c r="H234" s="236"/>
+      <c r="I234" s="236"/>
+      <c r="J234" s="236"/>
+      <c r="K234" s="236"/>
+    </row>
+    <row r="235" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F235" s="236"/>
+      <c r="G235" s="236"/>
+      <c r="H235" s="236"/>
+      <c r="I235" s="236"/>
+      <c r="J235" s="236"/>
+      <c r="K235" s="236"/>
+    </row>
+    <row r="236" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F236" s="236"/>
+      <c r="G236" s="236"/>
+      <c r="H236" s="236"/>
+      <c r="I236" s="236"/>
+      <c r="J236" s="236"/>
+      <c r="K236" s="236"/>
+    </row>
+    <row r="237" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F237" s="236"/>
+      <c r="G237" s="236"/>
+      <c r="H237" s="236"/>
+      <c r="I237" s="236"/>
+      <c r="J237" s="236"/>
+      <c r="K237" s="236"/>
+    </row>
+    <row r="238" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F238" s="236"/>
+      <c r="G238" s="236"/>
+      <c r="H238" s="236"/>
+      <c r="I238" s="236"/>
+      <c r="J238" s="236"/>
+      <c r="K238" s="236"/>
+    </row>
+    <row r="239" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F239" s="236"/>
+      <c r="G239" s="236"/>
+      <c r="H239" s="236"/>
+      <c r="I239" s="236"/>
+      <c r="J239" s="236"/>
+      <c r="K239" s="236"/>
+    </row>
+    <row r="240" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F240" s="236"/>
+      <c r="G240" s="236"/>
+      <c r="H240" s="236"/>
+      <c r="I240" s="236"/>
+      <c r="J240" s="236"/>
+      <c r="K240" s="236"/>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A241" s="230" t="s">
+        <v>604</v>
+      </c>
+      <c r="B241" s="230"/>
+      <c r="C241" s="230"/>
+      <c r="D241" s="230"/>
+      <c r="E241" s="230"/>
+      <c r="F241" s="229"/>
+      <c r="G241" s="229"/>
+      <c r="H241" s="229"/>
+      <c r="I241" s="229"/>
+      <c r="J241" s="229"/>
+      <c r="K241" s="231"/>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F242" s="236"/>
+      <c r="G242" s="236"/>
+      <c r="H242" s="236"/>
+      <c r="I242" s="236"/>
+      <c r="J242" s="236"/>
+      <c r="K242" s="236"/>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F243" s="236"/>
+      <c r="G243" s="236"/>
+      <c r="H243" s="236"/>
+      <c r="I243" s="236"/>
+      <c r="J243" s="236"/>
+      <c r="K243" s="236"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F244" s="236"/>
+      <c r="G244" s="236"/>
+      <c r="H244" s="236"/>
+      <c r="I244" s="236"/>
+      <c r="J244" s="236"/>
+      <c r="K244" s="236"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F1:P1"/>
+  <mergeCells count="9">
+    <mergeCell ref="A188:E188"/>
+    <mergeCell ref="A241:E241"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.3543307086614173" bottom="0.3543307086614173" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68D513C-AAB4-45B3-A236-E57180D92C9F}">
-  <dimension ref="A1:E115"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B3">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>398</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>272</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B10">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>403</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D11" t="s">
-        <v>329</v>
-      </c>
-      <c r="E11" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>405</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>398</v>
-      </c>
-      <c r="D12" t="s">
-        <v>329</v>
-      </c>
-      <c r="E12" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>408</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>268</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>410</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>268</v>
-      </c>
-      <c r="D15" t="s">
-        <v>329</v>
-      </c>
-      <c r="E15" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>412</v>
-      </c>
-      <c r="B16">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>270</v>
-      </c>
-      <c r="D16" t="s">
-        <v>329</v>
-      </c>
-      <c r="E16" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>414</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E17" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>281</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>268</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>417</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
-        <v>398</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>419</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>270</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>421</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>422</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>268</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>268</v>
-      </c>
-      <c r="D23" t="s">
-        <v>329</v>
-      </c>
-      <c r="E23" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>426</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>427</v>
-      </c>
-      <c r="D24" t="s">
-        <v>329</v>
-      </c>
-      <c r="E24" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>429</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>315</v>
-      </c>
-      <c r="D25" t="s">
-        <v>329</v>
-      </c>
-      <c r="E25" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>431</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>314</v>
-      </c>
-      <c r="D26" t="s">
-        <v>329</v>
-      </c>
-      <c r="E26" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>433</v>
-      </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>268</v>
-      </c>
-      <c r="D27" t="s">
-        <v>329</v>
-      </c>
-      <c r="E27" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>435</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>270</v>
-      </c>
-      <c r="D28" t="s">
-        <v>329</v>
-      </c>
-      <c r="E28" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>438</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>439</v>
-      </c>
-      <c r="D30">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>441</v>
-      </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>270</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>443</v>
-      </c>
-      <c r="B32">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>270</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>445</v>
-      </c>
-      <c r="B33">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>272</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>269</v>
-      </c>
-      <c r="B34">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>439</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>267</v>
-      </c>
-      <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35" t="s">
-        <v>272</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B36">
-        <v>6</v>
-      </c>
-      <c r="C36" t="s">
-        <v>268</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>450</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>439</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>279</v>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>452</v>
-      </c>
-      <c r="B39">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>453</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>270</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>456</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>313</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>458</v>
-      </c>
-      <c r="B42">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>314</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>460</v>
-      </c>
-      <c r="B43">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>461</v>
-      </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B44">
-        <v>4</v>
-      </c>
-      <c r="C44" t="s">
-        <v>439</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>463</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
-      </c>
-      <c r="C45" t="s">
-        <v>464</v>
-      </c>
-      <c r="D45" t="s">
-        <v>329</v>
-      </c>
-      <c r="E45" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>466</v>
-      </c>
-      <c r="B46">
-        <v>2</v>
-      </c>
-      <c r="C46" t="s">
-        <v>313</v>
-      </c>
-      <c r="D46" t="s">
-        <v>329</v>
-      </c>
-      <c r="E46" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>468</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>313</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>470</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
-        <v>295</v>
-      </c>
-      <c r="D48" t="s">
-        <v>329</v>
-      </c>
-      <c r="E48" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>472</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>292</v>
-      </c>
-      <c r="D49" t="s">
-        <v>329</v>
-      </c>
-      <c r="E49" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>271</v>
-      </c>
-      <c r="B51">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>270</v>
-      </c>
-      <c r="D51" t="s">
-        <v>329</v>
-      </c>
-      <c r="E51" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>277</v>
-      </c>
-      <c r="B52">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>313</v>
-      </c>
-      <c r="D52" t="s">
-        <v>329</v>
-      </c>
-      <c r="E52" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>477</v>
-      </c>
-      <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>313</v>
-      </c>
-      <c r="D53" t="s">
-        <v>329</v>
-      </c>
-      <c r="E53" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>479</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54" t="s">
-        <v>315</v>
-      </c>
-      <c r="D54" t="s">
-        <v>329</v>
-      </c>
-      <c r="E54" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>481</v>
-      </c>
-      <c r="B55">
-        <v>6</v>
-      </c>
-      <c r="C55" t="s">
-        <v>270</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>483</v>
-      </c>
-      <c r="B56">
-        <v>4</v>
-      </c>
-      <c r="C56" t="s">
-        <v>439</v>
-      </c>
-      <c r="D56">
-        <v>2</v>
-      </c>
-      <c r="E56" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>485</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57" t="s">
-        <v>453</v>
-      </c>
-      <c r="D57">
-        <v>2</v>
-      </c>
-      <c r="E57" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>487</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58" t="s">
-        <v>453</v>
-      </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>123</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59" t="s">
-        <v>427</v>
-      </c>
-      <c r="D59">
-        <v>2</v>
-      </c>
-      <c r="E59" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>489</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>315</v>
-      </c>
-      <c r="D60">
-        <v>2</v>
-      </c>
-      <c r="E60" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>491</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61" t="s">
-        <v>315</v>
-      </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>493</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62" t="s">
-        <v>427</v>
-      </c>
-      <c r="D62">
-        <v>3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>495</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>439</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>497</v>
-      </c>
-      <c r="B64">
-        <v>4</v>
-      </c>
-      <c r="C64" t="s">
-        <v>272</v>
-      </c>
-      <c r="D64" t="s">
-        <v>329</v>
-      </c>
-      <c r="E64" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>499</v>
-      </c>
-      <c r="B65">
-        <v>8</v>
-      </c>
-      <c r="C65" t="s">
-        <v>285</v>
-      </c>
-      <c r="D65" t="s">
-        <v>329</v>
-      </c>
-      <c r="E65" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>501</v>
-      </c>
-      <c r="B66">
-        <v>4</v>
-      </c>
-      <c r="C66" t="s">
-        <v>283</v>
-      </c>
-      <c r="D66" t="s">
-        <v>329</v>
-      </c>
-      <c r="E66" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>291</v>
-      </c>
-      <c r="B67">
-        <v>4</v>
-      </c>
-      <c r="C67" t="s">
-        <v>295</v>
-      </c>
-      <c r="D67" t="s">
-        <v>329</v>
-      </c>
-      <c r="E67" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>293</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68" t="s">
-        <v>295</v>
-      </c>
-      <c r="D68" t="s">
-        <v>329</v>
-      </c>
-      <c r="E68" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>505</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69" t="s">
-        <v>295</v>
-      </c>
-      <c r="D69" t="s">
-        <v>329</v>
-      </c>
-      <c r="E69" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>507</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70" t="s">
-        <v>295</v>
-      </c>
-      <c r="D70" t="s">
-        <v>329</v>
-      </c>
-      <c r="E70" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>509</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71" t="s">
-        <v>295</v>
-      </c>
-      <c r="D71" t="s">
-        <v>329</v>
-      </c>
-      <c r="E71" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>301</v>
-      </c>
-      <c r="B72">
-        <v>3</v>
-      </c>
-      <c r="C72" t="s">
-        <v>292</v>
-      </c>
-      <c r="D72" t="s">
-        <v>329</v>
-      </c>
-      <c r="E72" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>300</v>
-      </c>
-      <c r="B73">
-        <v>2</v>
-      </c>
-      <c r="C73" t="s">
-        <v>295</v>
-      </c>
-      <c r="D73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E73" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>299</v>
-      </c>
-      <c r="B74">
-        <v>4</v>
-      </c>
-      <c r="C74" t="s">
-        <v>295</v>
-      </c>
-      <c r="D74" t="s">
-        <v>329</v>
-      </c>
-      <c r="E74" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>515</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76" t="s">
-        <v>314</v>
-      </c>
-      <c r="D76">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>517</v>
-      </c>
-      <c r="B77">
-        <v>2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>453</v>
-      </c>
-      <c r="D77">
-        <v>3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>518</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
-        <v>292</v>
-      </c>
-      <c r="D78">
-        <v>3</v>
-      </c>
-      <c r="E78" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>520</v>
-      </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="C79" t="s">
-        <v>521</v>
-      </c>
-      <c r="D79">
-        <v>3</v>
-      </c>
-      <c r="E79" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>523</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80" t="s">
-        <v>524</v>
-      </c>
-      <c r="D80">
-        <v>4</v>
-      </c>
-      <c r="E80" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>526</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81" t="s">
-        <v>287</v>
-      </c>
-      <c r="D81" t="s">
-        <v>329</v>
-      </c>
-      <c r="E81" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>528</v>
-      </c>
-      <c r="B82">
-        <v>2</v>
-      </c>
-      <c r="C82" t="s">
-        <v>398</v>
-      </c>
-      <c r="D82" t="s">
-        <v>329</v>
-      </c>
-      <c r="E82" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>530</v>
-      </c>
-      <c r="B83">
-        <v>4</v>
-      </c>
-      <c r="C83" t="s">
-        <v>531</v>
-      </c>
-      <c r="D83" t="s">
-        <v>329</v>
-      </c>
-      <c r="E83" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>286</v>
-      </c>
-      <c r="B84">
-        <v>2</v>
-      </c>
-      <c r="C84" t="s">
-        <v>308</v>
-      </c>
-      <c r="D84" t="s">
-        <v>329</v>
-      </c>
-      <c r="E84" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>288</v>
-      </c>
-      <c r="B85">
-        <v>2</v>
-      </c>
-      <c r="C85" t="s">
-        <v>534</v>
-      </c>
-      <c r="D85" t="s">
-        <v>329</v>
-      </c>
-      <c r="E85" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>536</v>
-      </c>
-      <c r="B86">
-        <v>2</v>
-      </c>
-      <c r="C86" t="s">
-        <v>308</v>
-      </c>
-      <c r="D86" t="s">
-        <v>329</v>
-      </c>
-      <c r="E86" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>306</v>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87" t="s">
-        <v>534</v>
-      </c>
-      <c r="D87" t="s">
-        <v>329</v>
-      </c>
-      <c r="E87" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>290</v>
-      </c>
-      <c r="B88">
-        <v>2</v>
-      </c>
-      <c r="C88" t="s">
-        <v>308</v>
-      </c>
-      <c r="D88" t="s">
-        <v>329</v>
-      </c>
-      <c r="E88" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>540</v>
-      </c>
-      <c r="B89">
-        <v>2</v>
-      </c>
-      <c r="C89" t="s">
-        <v>541</v>
-      </c>
-      <c r="D89" t="s">
-        <v>329</v>
-      </c>
-      <c r="E89" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>543</v>
-      </c>
-      <c r="B90">
-        <v>2</v>
-      </c>
-      <c r="C90" t="s">
-        <v>544</v>
-      </c>
-      <c r="D90" t="s">
-        <v>329</v>
-      </c>
-      <c r="E90" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>294</v>
-      </c>
-      <c r="B91">
-        <v>2</v>
-      </c>
-      <c r="C91" t="s">
-        <v>289</v>
-      </c>
-      <c r="D91" t="s">
-        <v>329</v>
-      </c>
-      <c r="E91" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>296</v>
-      </c>
-      <c r="B92">
-        <v>2</v>
-      </c>
-      <c r="C92" t="s">
-        <v>289</v>
-      </c>
-      <c r="D92" t="s">
-        <v>329</v>
-      </c>
-      <c r="E92" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>548</v>
-      </c>
-      <c r="B93">
-        <v>2</v>
-      </c>
-      <c r="C93" t="s">
-        <v>289</v>
-      </c>
-      <c r="D93" t="s">
-        <v>329</v>
-      </c>
-      <c r="E93" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>550</v>
-      </c>
-      <c r="B94">
-        <v>2</v>
-      </c>
-      <c r="C94" t="s">
-        <v>289</v>
-      </c>
-      <c r="D94" t="s">
-        <v>329</v>
-      </c>
-      <c r="E94" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>552</v>
-      </c>
-      <c r="B95">
-        <v>2</v>
-      </c>
-      <c r="C95" t="s">
-        <v>289</v>
-      </c>
-      <c r="D95" t="s">
-        <v>329</v>
-      </c>
-      <c r="E95" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>554</v>
-      </c>
-      <c r="B96">
-        <v>2</v>
-      </c>
-      <c r="C96" t="s">
-        <v>308</v>
-      </c>
-      <c r="D96" t="s">
-        <v>329</v>
-      </c>
-      <c r="E96" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>297</v>
-      </c>
-      <c r="B97">
-        <v>2</v>
-      </c>
-      <c r="C97" t="s">
-        <v>308</v>
-      </c>
-      <c r="D97" t="s">
-        <v>329</v>
-      </c>
-      <c r="E97" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>298</v>
-      </c>
-      <c r="B98">
-        <v>2</v>
-      </c>
-      <c r="C98" t="s">
-        <v>308</v>
-      </c>
-      <c r="D98" t="s">
-        <v>329</v>
-      </c>
-      <c r="E98" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>558</v>
-      </c>
-      <c r="B99">
-        <v>2</v>
-      </c>
-      <c r="C99" t="s">
-        <v>308</v>
-      </c>
-      <c r="D99" t="s">
-        <v>329</v>
-      </c>
-      <c r="E99" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>561</v>
-      </c>
-      <c r="B101">
-        <v>2</v>
-      </c>
-      <c r="C101" t="s">
-        <v>562</v>
-      </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>564</v>
-      </c>
-      <c r="B102">
-        <v>2</v>
-      </c>
-      <c r="C102" t="s">
-        <v>565</v>
-      </c>
-      <c r="D102">
-        <v>2</v>
-      </c>
-      <c r="E102" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>567</v>
-      </c>
-      <c r="B103">
-        <v>2</v>
-      </c>
-      <c r="C103" t="s">
-        <v>562</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
-      </c>
-      <c r="E103" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>569</v>
-      </c>
-      <c r="B104">
-        <v>2</v>
-      </c>
-      <c r="C104" t="s">
-        <v>565</v>
-      </c>
-      <c r="D104">
-        <v>2</v>
-      </c>
-      <c r="E104" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>570</v>
-      </c>
-      <c r="B105">
-        <v>2</v>
-      </c>
-      <c r="C105" t="s">
-        <v>571</v>
-      </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>573</v>
-      </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106" t="s">
-        <v>574</v>
-      </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>576</v>
-      </c>
-      <c r="B107">
-        <v>4</v>
-      </c>
-      <c r="C107" t="s">
-        <v>534</v>
-      </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-      <c r="E107" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>578</v>
-      </c>
-      <c r="B108">
-        <v>2</v>
-      </c>
-      <c r="C108" t="s">
-        <v>565</v>
-      </c>
-      <c r="D108">
-        <v>2</v>
-      </c>
-      <c r="E108" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>579</v>
-      </c>
-      <c r="B109">
-        <v>1</v>
-      </c>
-      <c r="C109" t="s">
-        <v>580</v>
-      </c>
-      <c r="D109">
-        <v>3</v>
-      </c>
-      <c r="E109" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>581</v>
-      </c>
-      <c r="B110">
-        <v>2</v>
-      </c>
-      <c r="C110" t="s">
-        <v>562</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>583</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" t="s">
-        <v>584</v>
-      </c>
-      <c r="D111" t="s">
-        <v>329</v>
-      </c>
-      <c r="E111" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>586</v>
-      </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s">
-        <v>574</v>
-      </c>
-      <c r="D112">
-        <v>1</v>
-      </c>
-      <c r="E112" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>588</v>
-      </c>
-      <c r="B113">
-        <v>1</v>
-      </c>
-      <c r="C113" t="s">
-        <v>574</v>
-      </c>
-      <c r="D113">
-        <v>1</v>
-      </c>
-      <c r="E113" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>590</v>
-      </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114" t="s">
-        <v>565</v>
-      </c>
-      <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>592</v>
-      </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115" t="s">
-        <v>593</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115" t="s">
-        <v>594</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
